--- a/golf_recommendations.xlsx
+++ b/golf_recommendations.xlsx
@@ -511,7 +511,7 @@
         <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="G2" t="n">
         <v>2</v>
@@ -534,7 +534,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>5I</t>
         </is>
       </c>
     </row>
@@ -559,7 +559,7 @@
         <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
@@ -582,7 +582,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>8I</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -651,7 +651,7 @@
         <v>5</v>
       </c>
       <c r="F5" t="n">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -674,7 +674,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Layup (3H)</t>
+          <t>3W</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
         <v>4</v>
       </c>
       <c r="F6" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="G6" t="n">
         <v>2</v>
@@ -722,7 +722,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Layup (4I)</t>
+          <t>6I</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
         <v>4</v>
       </c>
       <c r="F7" t="n">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
@@ -770,7 +770,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>9I</t>
         </is>
       </c>
     </row>
@@ -795,7 +795,7 @@
         <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>302</v>
+        <v>282</v>
       </c>
       <c r="G8" t="n">
         <v>2</v>
@@ -818,7 +818,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Layup (3W)</t>
+          <t>Layup (6I)</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
         <v>4</v>
       </c>
       <c r="F10" t="n">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="G10" t="n">
         <v>3</v>
@@ -910,7 +910,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>PW</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
         <v>4</v>
       </c>
       <c r="F11" t="n">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="G11" t="n">
         <v>2</v>
@@ -958,7 +958,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>3H</t>
         </is>
       </c>
     </row>
@@ -983,7 +983,7 @@
         <v>4</v>
       </c>
       <c r="F12" t="n">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="G12" t="n">
         <v>2</v>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>3H</t>
+          <t>6I</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
         <v>4</v>
       </c>
       <c r="F13" t="n">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="G13" t="n">
         <v>2</v>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>3H</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
         <v>5</v>
       </c>
       <c r="F14" t="n">
-        <v>336</v>
+        <v>316</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>LAYUP</t>
+          <t>Layup (3W)</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>9I</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -1171,7 +1171,7 @@
         <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>207</v>
+        <v>187</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>5I</t>
         </is>
       </c>
     </row>
@@ -1219,7 +1219,7 @@
         <v>4</v>
       </c>
       <c r="F17" t="n">
-        <v>234</v>
+        <v>214</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Layup (3H)</t>
+          <t>3W</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
         <v>4</v>
       </c>
       <c r="F19" t="n">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="G19" t="n">
         <v>2</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>9I</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
         <v>4</v>
       </c>
       <c r="F20" t="n">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="G20" t="n">
         <v>2</v>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>3H</t>
         </is>
       </c>
     </row>
@@ -1407,7 +1407,7 @@
         <v>4</v>
       </c>
       <c r="F21" t="n">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="G21" t="n">
         <v>2</v>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>8I</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1455,7 @@
         <v>4</v>
       </c>
       <c r="F22" t="n">
-        <v>228</v>
+        <v>208</v>
       </c>
       <c r="G22" t="n">
         <v>2</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Layup (6I)</t>
+          <t>3H</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
         <v>4</v>
       </c>
       <c r="F23" t="n">
-        <v>218</v>
+        <v>198</v>
       </c>
       <c r="G23" t="n">
         <v>2</v>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>3H</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>5I</t>
+          <t>6I</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -1639,7 +1639,7 @@
         <v>5</v>
       </c>
       <c r="F26" t="n">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="G26" t="n">
         <v>2.2</v>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Layup (4I)</t>
+          <t>Layup (9I)</t>
         </is>
       </c>
     </row>
@@ -1687,7 +1687,7 @@
         <v>5</v>
       </c>
       <c r="F27" t="n">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="G27" t="n">
         <v>2</v>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Layup (4I)</t>
+          <t>Layup (5I)</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
         <v>4</v>
       </c>
       <c r="F28" t="n">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="G28" t="n">
         <v>1.8</v>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>D</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>LW</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
         <v>4</v>
       </c>
       <c r="F29" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="G29" t="n">
         <v>2</v>
@@ -1831,7 +1831,7 @@
         <v>4</v>
       </c>
       <c r="F30" t="n">
-        <v>239</v>
+        <v>219</v>
       </c>
       <c r="G30" t="n">
         <v>1.8</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Layup (3H)</t>
+          <t>3W</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
         <v>4</v>
       </c>
       <c r="F31" t="n">
-        <v>223</v>
+        <v>203</v>
       </c>
       <c r="G31" t="n">
         <v>2</v>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Layup (4I)</t>
+          <t>3H</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>3H</t>
+          <t>5I</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>6I</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
         <v>5</v>
       </c>
       <c r="F34" t="n">
-        <v>342</v>
+        <v>322</v>
       </c>
       <c r="G34" t="n">
         <v>2.4</v>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>LAYUP</t>
+          <t>Layup (3W)</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
         <v>5</v>
       </c>
       <c r="F35" t="n">
-        <v>322</v>
+        <v>302</v>
       </c>
       <c r="G35" t="n">
         <v>1</v>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>LAYUP</t>
+          <t>Layup (3H)</t>
         </is>
       </c>
     </row>
@@ -2111,7 +2111,7 @@
         <v>4</v>
       </c>
       <c r="F36" t="n">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="G36" t="n">
         <v>1.6</v>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -2159,7 +2159,7 @@
         <v>4</v>
       </c>
       <c r="F37" t="n">
-        <v>139</v>
+        <v>105</v>
       </c>
       <c r="G37" t="n">
         <v>1</v>
@@ -2177,12 +2177,12 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>D</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>SW</t>
         </is>
       </c>
     </row>
@@ -2207,7 +2207,7 @@
         <v>4</v>
       </c>
       <c r="F38" t="n">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="G38" t="n">
         <v>2</v>
@@ -2230,7 +2230,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>PW</t>
         </is>
       </c>
     </row>
@@ -2255,7 +2255,7 @@
         <v>4</v>
       </c>
       <c r="F39" t="n">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="G39" t="n">
         <v>2</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>LAYUP (4I)</t>
+          <t>3H</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>3H</t>
+          <t>5I</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
@@ -2391,7 +2391,7 @@
         <v>5</v>
       </c>
       <c r="F42" t="n">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="G42" t="n">
         <v>2</v>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>LAYUP</t>
+          <t>Layup (6I)</t>
         </is>
       </c>
     </row>
@@ -2439,7 +2439,7 @@
         <v>5</v>
       </c>
       <c r="F43" t="n">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="G43" t="n">
         <v>2</v>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Layup (3H)</t>
+          <t>3W</t>
         </is>
       </c>
     </row>
@@ -2487,7 +2487,7 @@
         <v>4</v>
       </c>
       <c r="F44" t="n">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="G44" t="n">
         <v>2</v>
@@ -2510,7 +2510,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -2535,7 +2535,7 @@
         <v>4</v>
       </c>
       <c r="F45" t="n">
-        <v>138</v>
+        <v>104</v>
       </c>
       <c r="G45" t="n">
         <v>2</v>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>D</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>SW</t>
         </is>
       </c>
     </row>
@@ -2583,7 +2583,7 @@
         <v>4</v>
       </c>
       <c r="F46" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="G46" t="n">
         <v>1.8</v>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>PW</t>
         </is>
       </c>
     </row>
@@ -2631,7 +2631,7 @@
         <v>4</v>
       </c>
       <c r="F47" t="n">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="G47" t="n">
         <v>2</v>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -2679,7 +2679,7 @@
         <v>4</v>
       </c>
       <c r="F48" t="n">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="G48" t="n">
         <v>1.6</v>
@@ -2702,7 +2702,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>9I</t>
         </is>
       </c>
     </row>
@@ -2727,7 +2727,7 @@
         <v>4</v>
       </c>
       <c r="F49" t="n">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="G49" t="n">
         <v>2</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>9I</t>
+          <t>PW</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
         <v>5</v>
       </c>
       <c r="F50" t="n">
-        <v>278</v>
+        <v>258</v>
       </c>
       <c r="G50" t="n">
         <v>2</v>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Layup (6I)</t>
+          <t>Layup (8I)</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
         <v>5</v>
       </c>
       <c r="F51" t="n">
-        <v>267</v>
+        <v>247</v>
       </c>
       <c r="G51" t="n">
         <v>2</v>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Layup (4I)</t>
+          <t>Layup (3H)</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>6I</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>8I</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
@@ -2959,7 +2959,7 @@
         <v>4</v>
       </c>
       <c r="F54" t="n">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="G54" t="n">
         <v>1.6</v>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>9I</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -3007,7 +3007,7 @@
         <v>4</v>
       </c>
       <c r="F55" t="n">
-        <v>142</v>
+        <v>108</v>
       </c>
       <c r="G55" t="n">
         <v>2</v>
@@ -3025,12 +3025,12 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>D</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>9I</t>
+          <t>SW</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
         <v>4</v>
       </c>
       <c r="F56" t="n">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="G56" t="n">
         <v>1.83</v>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
         <v>4</v>
       </c>
       <c r="F57" t="n">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="G57" t="n">
         <v>1.75</v>
@@ -3126,7 +3126,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>SW</t>
         </is>
       </c>
     </row>
@@ -3151,7 +3151,7 @@
         <v>4</v>
       </c>
       <c r="F58" t="n">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="G58" t="n">
         <v>1.83</v>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>PW</t>
         </is>
       </c>
     </row>
@@ -3199,7 +3199,7 @@
         <v>4</v>
       </c>
       <c r="F59" t="n">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="G59" t="n">
         <v>2</v>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>9I</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>9I</t>
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
@@ -3335,7 +3335,7 @@
         <v>4</v>
       </c>
       <c r="F62" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="G62" t="n">
         <v>2</v>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
         <v>4</v>
       </c>
       <c r="F63" t="n">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="G63" t="n">
         <v>2</v>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>SW</t>
         </is>
       </c>
     </row>
@@ -3431,7 +3431,7 @@
         <v>4</v>
       </c>
       <c r="F64" t="n">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="G64" t="n">
         <v>1.67</v>
@@ -3454,7 +3454,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>6I</t>
+          <t>8I</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
         <v>4</v>
       </c>
       <c r="F65" t="n">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="G65" t="n">
         <v>1.25</v>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>9I</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3615,7 @@
         <v>5</v>
       </c>
       <c r="F68" t="n">
-        <v>284</v>
+        <v>264</v>
       </c>
       <c r="G68" t="n">
         <v>2</v>
@@ -3638,7 +3638,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Layup (3H)</t>
+          <t>Layup (8I)</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
         <v>5</v>
       </c>
       <c r="F69" t="n">
-        <v>277</v>
+        <v>257</v>
       </c>
       <c r="G69" t="n">
         <v>2</v>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Layup (6I)</t>
+          <t>Layup (8I)</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
         <v>4</v>
       </c>
       <c r="F70" t="n">
-        <v>138</v>
+        <v>104</v>
       </c>
       <c r="G70" t="n">
         <v>1.83</v>
@@ -3729,12 +3729,12 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>D</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>SW</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
         <v>4</v>
       </c>
       <c r="F71" t="n">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="G71" t="n">
         <v>1.75</v>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>SW</t>
         </is>
       </c>
     </row>
@@ -3807,7 +3807,7 @@
         <v>5</v>
       </c>
       <c r="F72" t="n">
-        <v>337</v>
+        <v>317</v>
       </c>
       <c r="G72" t="n">
         <v>2.17</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>LAYUP</t>
+          <t>Layup (3W)</t>
         </is>
       </c>
     </row>
@@ -3855,7 +3855,7 @@
         <v>5</v>
       </c>
       <c r="F73" t="n">
-        <v>309</v>
+        <v>289</v>
       </c>
       <c r="G73" t="n">
         <v>1.75</v>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Layup (3W)</t>
+          <t>Layup (3H)</t>
         </is>
       </c>
     </row>
@@ -3903,7 +3903,7 @@
         <v>4</v>
       </c>
       <c r="F74" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="G74" t="n">
         <v>1.5</v>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>SW</t>
         </is>
       </c>
     </row>
@@ -3951,7 +3951,7 @@
         <v>4</v>
       </c>
       <c r="F75" t="n">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="G75" t="n">
         <v>1.5</v>
@@ -3969,12 +3969,12 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>D</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>SW</t>
         </is>
       </c>
     </row>
@@ -4017,7 +4017,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>7I</t>
         </is>
       </c>
       <c r="L76" t="inlineStr"/>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>8I</t>
         </is>
       </c>
       <c r="L77" t="inlineStr"/>
@@ -4087,7 +4087,7 @@
         <v>4</v>
       </c>
       <c r="F78" t="n">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="G78" t="n">
         <v>2</v>
@@ -4135,7 +4135,7 @@
         <v>4</v>
       </c>
       <c r="F79" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="G79" t="n">
         <v>1.5</v>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>3W</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -4183,7 +4183,7 @@
         <v>5</v>
       </c>
       <c r="F80" t="n">
-        <v>349</v>
+        <v>329</v>
       </c>
       <c r="G80" t="n">
         <v>2.17</v>
@@ -4206,7 +4206,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>LAYUP</t>
+          <t>Layup (3W)</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
         <v>5</v>
       </c>
       <c r="F81" t="n">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="G81" t="n">
         <v>1.75</v>
@@ -4254,7 +4254,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>LAYUP</t>
+          <t>Layup (3H)</t>
         </is>
       </c>
     </row>
@@ -4279,7 +4279,7 @@
         <v>4</v>
       </c>
       <c r="F82" t="n">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="G82" t="n">
         <v>2.17</v>
@@ -4302,7 +4302,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>9I</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -4327,7 +4327,7 @@
         <v>4</v>
       </c>
       <c r="F83" t="n">
-        <v>143</v>
+        <v>109</v>
       </c>
       <c r="G83" t="n">
         <v>2</v>
@@ -4345,12 +4345,12 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>D</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>9I</t>
+          <t>SW</t>
         </is>
       </c>
     </row>
@@ -4393,7 +4393,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>3H</t>
         </is>
       </c>
       <c r="L84" t="inlineStr"/>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>8I</t>
         </is>
       </c>
       <c r="L85" t="inlineStr"/>
@@ -4463,7 +4463,7 @@
         <v>4</v>
       </c>
       <c r="F86" t="n">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="G86" t="n">
         <v>1.67</v>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -4511,7 +4511,7 @@
         <v>4</v>
       </c>
       <c r="F87" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="G87" t="n">
         <v>1.75</v>
@@ -4534,7 +4534,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>SW</t>
         </is>
       </c>
     </row>
@@ -4559,7 +4559,7 @@
         <v>4</v>
       </c>
       <c r="F88" t="n">
-        <v>195</v>
+        <v>175</v>
       </c>
       <c r="G88" t="n">
         <v>1.67</v>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>3H</t>
+          <t>6I</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4607,7 @@
         <v>4</v>
       </c>
       <c r="F89" t="n">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="G89" t="n">
         <v>1.75</v>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>3H</t>
+          <t>8I</t>
         </is>
       </c>
     </row>
@@ -4655,7 +4655,7 @@
         <v>4</v>
       </c>
       <c r="F90" t="n">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="G90" t="n">
         <v>1.83</v>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>8I</t>
         </is>
       </c>
     </row>
@@ -4703,7 +4703,7 @@
         <v>4</v>
       </c>
       <c r="F91" t="n">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="G91" t="n">
         <v>1.5</v>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>9I</t>
         </is>
       </c>
     </row>
@@ -4751,7 +4751,7 @@
         <v>4</v>
       </c>
       <c r="F92" t="n">
-        <v>248</v>
+        <v>228</v>
       </c>
       <c r="G92" t="n">
         <v>2</v>
@@ -4774,7 +4774,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>Layup (3H)</t>
+          <t>3W</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
         <v>4</v>
       </c>
       <c r="F93" t="n">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="G93" t="n">
         <v>1</v>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>Layup (3H)</t>
+          <t>3W</t>
         </is>
       </c>
     </row>
@@ -4847,7 +4847,7 @@
         <v>4</v>
       </c>
       <c r="F94" t="n">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="G94" t="n">
         <v>1.5</v>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>6I</t>
+          <t>8I</t>
         </is>
       </c>
     </row>
@@ -4895,7 +4895,7 @@
         <v>4</v>
       </c>
       <c r="F95" t="n">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="G95" t="n">
         <v>2</v>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>9I</t>
         </is>
       </c>
     </row>
@@ -4943,7 +4943,7 @@
         <v>4</v>
       </c>
       <c r="F96" t="n">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="G96" t="n">
         <v>1.5</v>
@@ -4966,7 +4966,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>PW</t>
         </is>
       </c>
     </row>
@@ -4991,7 +4991,7 @@
         <v>4</v>
       </c>
       <c r="F97" t="n">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="G97" t="n">
         <v>2</v>
@@ -5014,7 +5014,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>9I</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>5I</t>
+          <t>6I</t>
         </is>
       </c>
       <c r="L98" t="inlineStr"/>
@@ -5101,7 +5101,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>8I</t>
         </is>
       </c>
       <c r="L99" t="inlineStr"/>
@@ -5127,7 +5127,7 @@
         <v>5</v>
       </c>
       <c r="F100" t="n">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="G100" t="n">
         <v>2</v>
@@ -5150,7 +5150,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>Layup (3W)</t>
+          <t>Layup (5I)</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
         <v>5</v>
       </c>
       <c r="F101" t="n">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="G101" t="n">
         <v>1</v>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>Layup (3H)</t>
+          <t>Layup (7I)</t>
         </is>
       </c>
     </row>
@@ -5223,7 +5223,7 @@
         <v>4</v>
       </c>
       <c r="F102" t="n">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="G102" t="n">
         <v>2</v>
@@ -5241,12 +5241,12 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>D</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>9I</t>
+          <t>SW</t>
         </is>
       </c>
     </row>
@@ -5271,7 +5271,7 @@
         <v>4</v>
       </c>
       <c r="F103" t="n">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="G103" t="n">
         <v>2</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>SW</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>3H</t>
+          <t>5I</t>
         </is>
       </c>
       <c r="L104" t="inlineStr"/>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>8I</t>
         </is>
       </c>
       <c r="L105" t="inlineStr"/>
@@ -5407,7 +5407,7 @@
         <v>4</v>
       </c>
       <c r="F106" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="G106" t="n">
         <v>1.5</v>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>5I</t>
+          <t>8I</t>
         </is>
       </c>
     </row>
@@ -5455,7 +5455,7 @@
         <v>4</v>
       </c>
       <c r="F107" t="n">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="G107" t="n">
         <v>2</v>
@@ -5478,7 +5478,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>PW</t>
         </is>
       </c>
     </row>
@@ -5503,7 +5503,7 @@
         <v>4</v>
       </c>
       <c r="F108" t="n">
-        <v>243</v>
+        <v>223</v>
       </c>
       <c r="G108" t="n">
         <v>2</v>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>Layup (3H)</t>
+          <t>3W</t>
         </is>
       </c>
     </row>
@@ -5551,7 +5551,7 @@
         <v>4</v>
       </c>
       <c r="F109" t="n">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="G109" t="n">
         <v>2</v>
@@ -5574,7 +5574,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>Layup (4I)</t>
+          <t>3H</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
         <v>4</v>
       </c>
       <c r="F110" t="n">
-        <v>228</v>
+        <v>208</v>
       </c>
       <c r="G110" t="n">
         <v>1.5</v>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>Layup (6I)</t>
+          <t>3H</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5647,7 @@
         <v>4</v>
       </c>
       <c r="F111" t="n">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="G111" t="n">
         <v>1</v>
@@ -5670,7 +5670,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>3H</t>
+          <t>6I</t>
         </is>
       </c>
     </row>
@@ -5695,7 +5695,7 @@
         <v>4</v>
       </c>
       <c r="F112" t="n">
-        <v>239</v>
+        <v>219</v>
       </c>
       <c r="G112" t="n">
         <v>1</v>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>Layup (3H)</t>
+          <t>3W</t>
         </is>
       </c>
     </row>
@@ -5743,7 +5743,7 @@
         <v>4</v>
       </c>
       <c r="F113" t="n">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="G113" t="n">
         <v>2</v>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>3H</t>
         </is>
       </c>
     </row>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>3H</t>
         </is>
       </c>
       <c r="L114" t="inlineStr"/>
@@ -5879,7 +5879,7 @@
         <v>4</v>
       </c>
       <c r="F116" t="n">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="G116" t="n">
         <v>1.5</v>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>6I</t>
+          <t>8I</t>
         </is>
       </c>
     </row>
@@ -5927,7 +5927,7 @@
         <v>4</v>
       </c>
       <c r="F117" t="n">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="G117" t="n">
         <v>2</v>
@@ -5950,7 +5950,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>PW</t>
         </is>
       </c>
     </row>
@@ -5975,7 +5975,7 @@
         <v>4</v>
       </c>
       <c r="F118" t="n">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="G118" t="n">
         <v>1.5</v>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>3H</t>
         </is>
       </c>
     </row>
@@ -6023,7 +6023,7 @@
         <v>4</v>
       </c>
       <c r="F119" t="n">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="G119" t="n">
         <v>2</v>
@@ -6046,7 +6046,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>3H</t>
+          <t>6I</t>
         </is>
       </c>
     </row>
@@ -6071,7 +6071,7 @@
         <v>4</v>
       </c>
       <c r="F120" t="n">
-        <v>227</v>
+        <v>207</v>
       </c>
       <c r="G120" t="n">
         <v>2</v>
@@ -6094,7 +6094,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>Layup (6I)</t>
+          <t>3H</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
         <v>4</v>
       </c>
       <c r="F121" t="n">
-        <v>215</v>
+        <v>195</v>
       </c>
       <c r="G121" t="n">
         <v>1</v>
@@ -6142,7 +6142,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>3H</t>
         </is>
       </c>
     </row>
@@ -6167,7 +6167,7 @@
         <v>5</v>
       </c>
       <c r="F122" t="n">
-        <v>342</v>
+        <v>322</v>
       </c>
       <c r="G122" t="n">
         <v>2</v>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>LAYUP</t>
+          <t>Layup (3W)</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
         <v>5</v>
       </c>
       <c r="F123" t="n">
-        <v>312</v>
+        <v>292</v>
       </c>
       <c r="G123" t="n">
         <v>1</v>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>Layup (3W)</t>
+          <t>Layup (3H)</t>
         </is>
       </c>
     </row>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>8I</t>
         </is>
       </c>
       <c r="L124" t="inlineStr"/>
@@ -6325,7 +6325,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>9I</t>
         </is>
       </c>
       <c r="L125" t="inlineStr"/>
@@ -6351,7 +6351,7 @@
         <v>4</v>
       </c>
       <c r="F126" t="n">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="G126" t="n">
         <v>1.5</v>
@@ -6374,7 +6374,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>3H</t>
+          <t>6I</t>
         </is>
       </c>
     </row>
@@ -6399,7 +6399,7 @@
         <v>4</v>
       </c>
       <c r="F127" t="n">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="G127" t="n">
         <v>2</v>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>6I</t>
+          <t>8I</t>
         </is>
       </c>
     </row>
@@ -6447,7 +6447,7 @@
         <v>4</v>
       </c>
       <c r="F128" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="G128" t="n">
         <v>2.6</v>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>9I</t>
         </is>
       </c>
     </row>
@@ -6495,7 +6495,7 @@
         <v>4</v>
       </c>
       <c r="F129" t="n">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="G129" t="n">
         <v>2</v>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>PW</t>
         </is>
       </c>
     </row>
@@ -6543,7 +6543,7 @@
         <v>4</v>
       </c>
       <c r="F130" t="n">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="G130" t="n">
         <v>2.4</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>8I</t>
         </is>
       </c>
     </row>
@@ -6591,7 +6591,7 @@
         <v>4</v>
       </c>
       <c r="F131" t="n">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="G131" t="n">
         <v>2</v>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>9I</t>
         </is>
       </c>
     </row>
@@ -6639,7 +6639,7 @@
         <v>4</v>
       </c>
       <c r="F132" t="n">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="G132" t="n">
         <v>2</v>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>9I</t>
         </is>
       </c>
     </row>
@@ -6687,7 +6687,7 @@
         <v>4</v>
       </c>
       <c r="F133" t="n">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="G133" t="n">
         <v>2</v>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>9I</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -6753,7 +6753,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>7I</t>
         </is>
       </c>
       <c r="L134" t="inlineStr"/>
@@ -6797,7 +6797,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>9I</t>
         </is>
       </c>
       <c r="L135" t="inlineStr"/>
@@ -6823,7 +6823,7 @@
         <v>4</v>
       </c>
       <c r="F136" t="n">
-        <v>138</v>
+        <v>104</v>
       </c>
       <c r="G136" t="n">
         <v>2</v>
@@ -6841,12 +6841,12 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>D</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>SW</t>
         </is>
       </c>
     </row>
@@ -6871,7 +6871,7 @@
         <v>4</v>
       </c>
       <c r="F137" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="G137" t="n">
         <v>1</v>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>SW</t>
         </is>
       </c>
     </row>
@@ -6919,7 +6919,7 @@
         <v>5</v>
       </c>
       <c r="F138" t="n">
-        <v>264</v>
+        <v>244</v>
       </c>
       <c r="G138" t="n">
         <v>1.8</v>
@@ -6942,7 +6942,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>Layup (4I)</t>
+          <t>Layup (3H)</t>
         </is>
       </c>
     </row>
@@ -6967,7 +6967,7 @@
         <v>5</v>
       </c>
       <c r="F139" t="n">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="G139" t="n">
         <v>2</v>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>Layup (4I)</t>
+          <t>Layup (6I)</t>
         </is>
       </c>
     </row>
@@ -7033,7 +7033,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>6I</t>
         </is>
       </c>
       <c r="L140" t="inlineStr"/>
@@ -7077,7 +7077,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>8I</t>
         </is>
       </c>
       <c r="L141" t="inlineStr"/>
@@ -7103,7 +7103,7 @@
         <v>4</v>
       </c>
       <c r="F142" t="n">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="G142" t="n">
         <v>2</v>
@@ -7126,7 +7126,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -7151,7 +7151,7 @@
         <v>4</v>
       </c>
       <c r="F143" t="n">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="G143" t="n">
         <v>2</v>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>SW</t>
         </is>
       </c>
     </row>
@@ -7199,7 +7199,7 @@
         <v>4</v>
       </c>
       <c r="F144" t="n">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="G144" t="n">
         <v>2</v>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>9I</t>
         </is>
       </c>
     </row>
@@ -7247,7 +7247,7 @@
         <v>4</v>
       </c>
       <c r="F145" t="n">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="G145" t="n">
         <v>1</v>
@@ -7270,7 +7270,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>PW</t>
         </is>
       </c>
     </row>
@@ -7295,7 +7295,7 @@
         <v>5</v>
       </c>
       <c r="F146" t="n">
-        <v>301</v>
+        <v>281</v>
       </c>
       <c r="G146" t="n">
         <v>1.6</v>
@@ -7318,7 +7318,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>Layup (3W)</t>
+          <t>Layup (6I)</t>
         </is>
       </c>
     </row>
@@ -7343,7 +7343,7 @@
         <v>5</v>
       </c>
       <c r="F147" t="n">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="G147" t="n">
         <v>2</v>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>Layup (3H)</t>
+          <t>Layup (7I)</t>
         </is>
       </c>
     </row>
@@ -7453,7 +7453,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>6I</t>
         </is>
       </c>
       <c r="L149" t="inlineStr"/>
@@ -7479,7 +7479,7 @@
         <v>4</v>
       </c>
       <c r="F150" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="G150" t="n">
         <v>2</v>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>LW</t>
         </is>
       </c>
     </row>
@@ -7527,7 +7527,7 @@
         <v>4</v>
       </c>
       <c r="F151" t="n">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="G151" t="n">
         <v>2</v>
@@ -7575,7 +7575,7 @@
         <v>4</v>
       </c>
       <c r="F152" t="n">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="G152" t="n">
         <v>2</v>
@@ -7598,7 +7598,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>5I</t>
         </is>
       </c>
     </row>
@@ -7623,7 +7623,7 @@
         <v>4</v>
       </c>
       <c r="F153" t="n">
-        <v>187</v>
+        <v>167</v>
       </c>
       <c r="G153" t="n">
         <v>2</v>
@@ -7646,7 +7646,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>3H</t>
+          <t>7I</t>
         </is>
       </c>
     </row>
@@ -7759,7 +7759,7 @@
         <v>4</v>
       </c>
       <c r="F156" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="G156" t="n">
         <v>1.8</v>
@@ -7782,7 +7782,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -7807,7 +7807,7 @@
         <v>4</v>
       </c>
       <c r="F157" t="n">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="G157" t="n">
         <v>1</v>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -7855,7 +7855,7 @@
         <v>4</v>
       </c>
       <c r="F158" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="G158" t="n">
         <v>2</v>
@@ -7878,7 +7878,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -7903,7 +7903,7 @@
         <v>4</v>
       </c>
       <c r="F159" t="n">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="G159" t="n">
         <v>2</v>
@@ -7951,7 +7951,7 @@
         <v>5</v>
       </c>
       <c r="F160" t="n">
-        <v>262</v>
+        <v>242</v>
       </c>
       <c r="G160" t="n">
         <v>2</v>
@@ -7974,7 +7974,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>Layup (4I)</t>
+          <t>Layup (3H)</t>
         </is>
       </c>
     </row>
@@ -7999,7 +7999,7 @@
         <v>5</v>
       </c>
       <c r="F161" t="n">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="G161" t="n">
         <v>2</v>
@@ -8022,7 +8022,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>Layup (4I)</t>
+          <t>Layup (6I)</t>
         </is>
       </c>
     </row>
@@ -8047,7 +8047,7 @@
         <v>4</v>
       </c>
       <c r="F162" t="n">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="G162" t="n">
         <v>2</v>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>9I</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -8095,7 +8095,7 @@
         <v>4</v>
       </c>
       <c r="F163" t="n">
-        <v>138</v>
+        <v>104</v>
       </c>
       <c r="G163" t="n">
         <v>2</v>
@@ -8113,12 +8113,12 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>D</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>SW</t>
         </is>
       </c>
     </row>
@@ -8143,7 +8143,7 @@
         <v>5</v>
       </c>
       <c r="F164" t="n">
-        <v>266</v>
+        <v>246</v>
       </c>
       <c r="G164" t="n">
         <v>1.75</v>
@@ -8166,7 +8166,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>Layup (4I)</t>
+          <t>Layup (3H)</t>
         </is>
       </c>
     </row>
@@ -8191,7 +8191,7 @@
         <v>5</v>
       </c>
       <c r="F165" t="n">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="G165" t="n">
         <v>2</v>
@@ -8214,7 +8214,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>3H</t>
         </is>
       </c>
     </row>
@@ -8239,7 +8239,7 @@
         <v>4</v>
       </c>
       <c r="F166" t="n">
-        <v>163</v>
+        <v>129</v>
       </c>
       <c r="G166" t="n">
         <v>1.75</v>
@@ -8257,12 +8257,12 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>D</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>PW</t>
         </is>
       </c>
     </row>
@@ -8287,7 +8287,7 @@
         <v>4</v>
       </c>
       <c r="F167" t="n">
-        <v>93</v>
+        <v>59</v>
       </c>
       <c r="G167" t="n">
         <v>1</v>
@@ -8305,12 +8305,12 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>D</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>LW</t>
         </is>
       </c>
     </row>
@@ -8353,7 +8353,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>5I</t>
+          <t>6I</t>
         </is>
       </c>
       <c r="L168" t="inlineStr"/>
@@ -8397,7 +8397,7 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>7I</t>
         </is>
       </c>
       <c r="L169" t="inlineStr"/>
@@ -8423,7 +8423,7 @@
         <v>5</v>
       </c>
       <c r="F170" t="n">
-        <v>274</v>
+        <v>254</v>
       </c>
       <c r="G170" t="n">
         <v>1.75</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>Layup (4I)</t>
+          <t>Layup (8I)</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
         <v>5</v>
       </c>
       <c r="F171" t="n">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="G171" t="n">
         <v>2</v>
@@ -8494,7 +8494,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>Layup (4I)</t>
+          <t>Layup (3H)</t>
         </is>
       </c>
     </row>
@@ -8537,7 +8537,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>9I</t>
         </is>
       </c>
       <c r="L172" t="inlineStr"/>
@@ -8607,7 +8607,7 @@
         <v>4</v>
       </c>
       <c r="F174" t="n">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="G174" t="n">
         <v>1.75</v>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>9I</t>
         </is>
       </c>
     </row>
@@ -8655,7 +8655,7 @@
         <v>4</v>
       </c>
       <c r="F175" t="n">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="G175" t="n">
         <v>1</v>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>PW</t>
         </is>
       </c>
     </row>
@@ -8703,7 +8703,7 @@
         <v>4</v>
       </c>
       <c r="F176" t="n">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="G176" t="n">
         <v>2</v>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>9I</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -8751,7 +8751,7 @@
         <v>4</v>
       </c>
       <c r="F177" t="n">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="G177" t="n">
         <v>2</v>
@@ -8769,12 +8769,12 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>D</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>9I</t>
+          <t>SW</t>
         </is>
       </c>
     </row>
@@ -8799,7 +8799,7 @@
         <v>4</v>
       </c>
       <c r="F178" t="n">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="G178" t="n">
         <v>1.75</v>
@@ -8817,12 +8817,12 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>D</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>LW</t>
         </is>
       </c>
     </row>
@@ -8847,7 +8847,7 @@
         <v>4</v>
       </c>
       <c r="F179" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G179" t="n">
         <v>1</v>
@@ -8865,7 +8865,7 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>3W</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -8895,7 +8895,7 @@
         <v>4</v>
       </c>
       <c r="F180" t="n">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="G180" t="n">
         <v>2</v>
@@ -8918,7 +8918,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>SW</t>
         </is>
       </c>
     </row>
@@ -8943,7 +8943,7 @@
         <v>4</v>
       </c>
       <c r="F181" t="n">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="G181" t="n">
         <v>2</v>
@@ -8961,12 +8961,12 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>D</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>LW</t>
         </is>
       </c>
     </row>
@@ -8991,7 +8991,7 @@
         <v>4</v>
       </c>
       <c r="F182" t="n">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="G182" t="n">
         <v>1.75</v>
@@ -9014,7 +9014,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -9039,7 +9039,7 @@
         <v>4</v>
       </c>
       <c r="F183" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="G183" t="n">
         <v>2</v>
@@ -9062,7 +9062,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>LW</t>
         </is>
       </c>
     </row>
@@ -9087,7 +9087,7 @@
         <v>4</v>
       </c>
       <c r="F184" t="n">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="G184" t="n">
         <v>1.5</v>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>LW</t>
         </is>
       </c>
     </row>
@@ -9135,7 +9135,7 @@
         <v>4</v>
       </c>
       <c r="F185" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G185" t="n">
         <v>1</v>
@@ -9153,7 +9153,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>3W</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -9183,7 +9183,7 @@
         <v>4</v>
       </c>
       <c r="F186" t="n">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="G186" t="n">
         <v>1.75</v>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>9I</t>
         </is>
       </c>
     </row>
@@ -9231,7 +9231,7 @@
         <v>4</v>
       </c>
       <c r="F187" t="n">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="G187" t="n">
         <v>1</v>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>9I</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -9279,7 +9279,7 @@
         <v>4</v>
       </c>
       <c r="F188" t="n">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="G188" t="n">
         <v>1.5</v>
@@ -9297,12 +9297,12 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>D</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>LW</t>
         </is>
       </c>
     </row>
@@ -9327,7 +9327,7 @@
         <v>4</v>
       </c>
       <c r="F189" t="n">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="G189" t="n">
         <v>2</v>
@@ -9393,7 +9393,7 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>7I</t>
         </is>
       </c>
       <c r="L190" t="inlineStr"/>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>8I</t>
         </is>
       </c>
       <c r="L191" t="inlineStr"/>
@@ -9463,7 +9463,7 @@
         <v>4</v>
       </c>
       <c r="F192" t="n">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="G192" t="n">
         <v>1.75</v>
@@ -9486,7 +9486,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>3H</t>
+          <t>6I</t>
         </is>
       </c>
     </row>
@@ -9511,7 +9511,7 @@
         <v>4</v>
       </c>
       <c r="F193" t="n">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="G193" t="n">
         <v>1</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>5I</t>
+          <t>8I</t>
         </is>
       </c>
     </row>
@@ -9559,7 +9559,7 @@
         <v>4</v>
       </c>
       <c r="F194" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="G194" t="n">
         <v>1.25</v>
@@ -9577,7 +9577,7 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>3W</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -9607,7 +9607,7 @@
         <v>4</v>
       </c>
       <c r="F195" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="G195" t="n">
         <v>2</v>
@@ -9630,7 +9630,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>LW - 50</t>
+          <t>LW</t>
         </is>
       </c>
     </row>
@@ -9655,7 +9655,7 @@
         <v>5</v>
       </c>
       <c r="F196" t="n">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="G196" t="n">
         <v>1.25</v>
@@ -9678,7 +9678,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>Layup (4I)</t>
+          <t>Layup (5I)</t>
         </is>
       </c>
     </row>
@@ -9703,7 +9703,7 @@
         <v>5</v>
       </c>
       <c r="F197" t="n">
-        <v>244</v>
+        <v>224</v>
       </c>
       <c r="G197" t="n">
         <v>2</v>
@@ -9726,7 +9726,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>Layup (3H)</t>
+          <t>3W</t>
         </is>
       </c>
     </row>
@@ -9751,7 +9751,7 @@
         <v>4</v>
       </c>
       <c r="F198" t="n">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="G198" t="n">
         <v>1.75</v>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>9I</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -9799,7 +9799,7 @@
         <v>4</v>
       </c>
       <c r="F199" t="n">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="G199" t="n">
         <v>1</v>
@@ -9822,7 +9822,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -9847,7 +9847,7 @@
         <v>4</v>
       </c>
       <c r="F200" t="n">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="G200" t="n">
         <v>3</v>
@@ -9870,7 +9870,7 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -9939,7 +9939,7 @@
         <v>5</v>
       </c>
       <c r="F202" t="n">
-        <v>312</v>
+        <v>292</v>
       </c>
       <c r="G202" t="n">
         <v>3</v>
@@ -9962,7 +9962,7 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>Layup (3W)</t>
+          <t>Layup (3H)</t>
         </is>
       </c>
     </row>
@@ -9987,7 +9987,7 @@
         <v>4</v>
       </c>
       <c r="F203" t="n">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="G203" t="n">
         <v>2</v>
@@ -10010,7 +10010,7 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>SW</t>
         </is>
       </c>
     </row>
@@ -10035,7 +10035,7 @@
         <v>4</v>
       </c>
       <c r="F204" t="n">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="G204" t="n">
         <v>2</v>
@@ -10053,12 +10053,12 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>D</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>9I</t>
+          <t>SW</t>
         </is>
       </c>
     </row>
@@ -10101,7 +10101,7 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>8I</t>
         </is>
       </c>
       <c r="L205" t="inlineStr"/>
@@ -10127,7 +10127,7 @@
         <v>4</v>
       </c>
       <c r="F206" t="n">
-        <v>183</v>
+        <v>163</v>
       </c>
       <c r="G206" t="n">
         <v>3</v>
@@ -10150,7 +10150,7 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>Layup (PW)</t>
+          <t>8I</t>
         </is>
       </c>
     </row>
@@ -10193,7 +10193,7 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>9I</t>
         </is>
       </c>
       <c r="L207" t="inlineStr"/>
@@ -10219,7 +10219,7 @@
         <v>5</v>
       </c>
       <c r="F208" t="n">
-        <v>295</v>
+        <v>275</v>
       </c>
       <c r="G208" t="n">
         <v>2</v>
@@ -10242,7 +10242,7 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>Layup (3H)</t>
+          <t>Layup (6I)</t>
         </is>
       </c>
     </row>
@@ -10267,7 +10267,7 @@
         <v>4</v>
       </c>
       <c r="F209" t="n">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="G209" t="n">
         <v>2</v>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>LW</t>
         </is>
       </c>
     </row>
@@ -10315,7 +10315,7 @@
         <v>4</v>
       </c>
       <c r="F210" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="G210" t="n">
         <v>2</v>
@@ -10338,7 +10338,7 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>LW</t>
         </is>
       </c>
     </row>
@@ -10363,7 +10363,7 @@
         <v>4</v>
       </c>
       <c r="F211" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="G211" t="n">
         <v>2</v>
@@ -10386,7 +10386,7 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>Layup (4I)</t>
+          <t>3H</t>
         </is>
       </c>
     </row>
@@ -10455,7 +10455,7 @@
         <v>4</v>
       </c>
       <c r="F213" t="n">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="G213" t="n">
         <v>2</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>6I</t>
         </is>
       </c>
     </row>
@@ -10503,7 +10503,7 @@
         <v>5</v>
       </c>
       <c r="F214" t="n">
-        <v>338</v>
+        <v>318</v>
       </c>
       <c r="G214" t="n">
         <v>2</v>
@@ -10526,7 +10526,7 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>LAYUP</t>
+          <t>Layup (3W)</t>
         </is>
       </c>
     </row>
@@ -10551,7 +10551,7 @@
         <v>4</v>
       </c>
       <c r="F215" t="n">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="G215" t="n">
         <v>2</v>
@@ -10617,7 +10617,7 @@
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>6I</t>
         </is>
       </c>
       <c r="L216" t="inlineStr"/>
@@ -10643,7 +10643,7 @@
         <v>5</v>
       </c>
       <c r="F217" t="n">
-        <v>302</v>
+        <v>282</v>
       </c>
       <c r="G217" t="n">
         <v>2</v>
@@ -10666,7 +10666,7 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>Layup (3W)</t>
+          <t>Layup (6I)</t>
         </is>
       </c>
     </row>
@@ -10691,7 +10691,7 @@
         <v>5</v>
       </c>
       <c r="F218" t="n">
-        <v>279</v>
+        <v>259</v>
       </c>
       <c r="G218" t="n">
         <v>2</v>
@@ -10714,7 +10714,7 @@
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>Layup (6I)</t>
+          <t>Layup (8I)</t>
         </is>
       </c>
     </row>
@@ -10757,7 +10757,7 @@
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>6I</t>
         </is>
       </c>
       <c r="L219" t="inlineStr"/>
@@ -10783,7 +10783,7 @@
         <v>4</v>
       </c>
       <c r="F220" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="G220" t="n">
         <v>2</v>
@@ -10806,7 +10806,7 @@
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -10831,7 +10831,7 @@
         <v>4</v>
       </c>
       <c r="F221" t="n">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="G221" t="n">
         <v>2</v>
@@ -10854,7 +10854,7 @@
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -10879,7 +10879,7 @@
         <v>4</v>
       </c>
       <c r="F222" t="n">
-        <v>217</v>
+        <v>197</v>
       </c>
       <c r="G222" t="n">
         <v>2</v>
@@ -10902,7 +10902,7 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>3H</t>
         </is>
       </c>
     </row>
@@ -10927,7 +10927,7 @@
         <v>5</v>
       </c>
       <c r="F223" t="n">
-        <v>217</v>
+        <v>197</v>
       </c>
       <c r="G223" t="n">
         <v>2</v>
@@ -10950,7 +10950,7 @@
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>3H</t>
         </is>
       </c>
     </row>
@@ -10975,7 +10975,7 @@
         <v>4</v>
       </c>
       <c r="F224" t="n">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="G224" t="n">
         <v>2</v>
@@ -10993,12 +10993,12 @@
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>D</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>LW</t>
         </is>
       </c>
     </row>
@@ -11041,7 +11041,7 @@
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>7I</t>
         </is>
       </c>
       <c r="L225" t="inlineStr"/>
@@ -11067,7 +11067,7 @@
         <v>5</v>
       </c>
       <c r="F226" t="n">
-        <v>244</v>
+        <v>224</v>
       </c>
       <c r="G226" t="n">
         <v>2</v>
@@ -11090,7 +11090,7 @@
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>Layup (3H)</t>
+          <t>3W</t>
         </is>
       </c>
     </row>
@@ -11115,7 +11115,7 @@
         <v>4</v>
       </c>
       <c r="F227" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="G227" t="n">
         <v>1</v>
@@ -11138,7 +11138,7 @@
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>3H</t>
         </is>
       </c>
     </row>
@@ -11163,7 +11163,7 @@
         <v>4</v>
       </c>
       <c r="F228" t="n">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="G228" t="n">
         <v>2</v>
@@ -11186,7 +11186,7 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>8I</t>
         </is>
       </c>
     </row>
@@ -11211,7 +11211,7 @@
         <v>4</v>
       </c>
       <c r="F229" t="n">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="G229" t="n">
         <v>2</v>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>SW</t>
         </is>
       </c>
     </row>
@@ -11259,7 +11259,7 @@
         <v>4</v>
       </c>
       <c r="F230" t="n">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="G230" t="n">
         <v>1</v>
@@ -11282,7 +11282,7 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -11307,7 +11307,7 @@
         <v>4</v>
       </c>
       <c r="F231" t="n">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="G231" t="n">
         <v>2</v>
@@ -11330,7 +11330,7 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>PW</t>
         </is>
       </c>
     </row>
@@ -11373,7 +11373,7 @@
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>7I</t>
         </is>
       </c>
       <c r="L232" t="inlineStr"/>
@@ -11399,7 +11399,7 @@
         <v>4</v>
       </c>
       <c r="F233" t="n">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="G233" t="n">
         <v>2</v>
@@ -11422,7 +11422,7 @@
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>3H</t>
+          <t>7I</t>
         </is>
       </c>
     </row>
@@ -11491,7 +11491,7 @@
         <v>4</v>
       </c>
       <c r="F235" t="n">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="G235" t="n">
         <v>2</v>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>5I</t>
         </is>
       </c>
     </row>
@@ -11539,7 +11539,7 @@
         <v>5</v>
       </c>
       <c r="F236" t="n">
-        <v>264</v>
+        <v>244</v>
       </c>
       <c r="G236" t="n">
         <v>2</v>
@@ -11562,7 +11562,7 @@
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>Layup (4I)</t>
+          <t>Layup (3H)</t>
         </is>
       </c>
     </row>
@@ -11587,7 +11587,7 @@
         <v>4</v>
       </c>
       <c r="F237" t="n">
-        <v>247</v>
+        <v>227</v>
       </c>
       <c r="G237" t="n">
         <v>2</v>
@@ -11610,7 +11610,7 @@
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>Layup (3H)</t>
+          <t>3W</t>
         </is>
       </c>
     </row>
@@ -11635,7 +11635,7 @@
         <v>4</v>
       </c>
       <c r="F238" t="n">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="G238" t="n">
         <v>2</v>
@@ -11658,7 +11658,7 @@
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>9I</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -11727,7 +11727,7 @@
         <v>4</v>
       </c>
       <c r="F240" t="n">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="G240" t="n">
         <v>1.5</v>
@@ -11750,7 +11750,7 @@
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -11775,7 +11775,7 @@
         <v>4</v>
       </c>
       <c r="F241" t="n">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="G241" t="n">
         <v>2</v>
@@ -11798,7 +11798,7 @@
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>PW</t>
         </is>
       </c>
     </row>
@@ -11823,7 +11823,7 @@
         <v>4</v>
       </c>
       <c r="F242" t="n">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="G242" t="n">
         <v>2.5</v>
@@ -11889,7 +11889,7 @@
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>3H</t>
         </is>
       </c>
       <c r="L243" t="inlineStr"/>
@@ -11915,7 +11915,7 @@
         <v>5</v>
       </c>
       <c r="F244" t="n">
-        <v>314</v>
+        <v>294</v>
       </c>
       <c r="G244" t="n">
         <v>1.5</v>
@@ -11938,7 +11938,7 @@
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>Layup (3W)</t>
+          <t>Layup (3H)</t>
         </is>
       </c>
     </row>
@@ -11963,7 +11963,7 @@
         <v>4</v>
       </c>
       <c r="F245" t="n">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="G245" t="n">
         <v>1</v>
@@ -11986,7 +11986,7 @@
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>Layup (4I)</t>
+          <t>3H</t>
         </is>
       </c>
     </row>
@@ -12011,7 +12011,7 @@
         <v>4</v>
       </c>
       <c r="F246" t="n">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="G246" t="n">
         <v>2.5</v>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>SW</t>
         </is>
       </c>
     </row>
@@ -12059,7 +12059,7 @@
         <v>5</v>
       </c>
       <c r="F247" t="n">
-        <v>306</v>
+        <v>286</v>
       </c>
       <c r="G247" t="n">
         <v>2.5</v>
@@ -12082,7 +12082,7 @@
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>Layup (3W)</t>
+          <t>Layup (5I)</t>
         </is>
       </c>
     </row>
@@ -12151,7 +12151,7 @@
         <v>4</v>
       </c>
       <c r="F249" t="n">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="G249" t="n">
         <v>1.5</v>
@@ -12174,7 +12174,7 @@
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>9I</t>
         </is>
       </c>
     </row>
@@ -12199,7 +12199,7 @@
         <v>4</v>
       </c>
       <c r="F250" t="n">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="G250" t="n">
         <v>2.5</v>
@@ -12222,7 +12222,7 @@
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>9I</t>
         </is>
       </c>
     </row>
@@ -12247,7 +12247,7 @@
         <v>4</v>
       </c>
       <c r="F251" t="n">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="G251" t="n">
         <v>2</v>
@@ -12270,7 +12270,7 @@
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>5I</t>
+          <t>8I</t>
         </is>
       </c>
     </row>
@@ -12339,7 +12339,7 @@
         <v>4</v>
       </c>
       <c r="F253" t="n">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="G253" t="n">
         <v>2</v>
@@ -12362,7 +12362,7 @@
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>5I</t>
+          <t>8I</t>
         </is>
       </c>
     </row>
@@ -12387,7 +12387,7 @@
         <v>5</v>
       </c>
       <c r="F254" t="n">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="G254" t="n">
         <v>3</v>
@@ -12410,7 +12410,7 @@
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>Layup (3H)</t>
+          <t>Layup (7I)</t>
         </is>
       </c>
     </row>
@@ -12453,7 +12453,7 @@
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>7I</t>
         </is>
       </c>
       <c r="L255" t="inlineStr"/>
@@ -12479,7 +12479,7 @@
         <v>4</v>
       </c>
       <c r="F256" t="n">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="G256" t="n">
         <v>3</v>
@@ -12502,7 +12502,7 @@
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>PW</t>
         </is>
       </c>
     </row>
@@ -12527,7 +12527,7 @@
         <v>5</v>
       </c>
       <c r="F257" t="n">
-        <v>303</v>
+        <v>283</v>
       </c>
       <c r="G257" t="n">
         <v>3</v>
@@ -12550,7 +12550,7 @@
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>Layup (3W)</t>
+          <t>Layup (5I)</t>
         </is>
       </c>
     </row>
@@ -12575,7 +12575,7 @@
         <v>4</v>
       </c>
       <c r="F258" t="n">
-        <v>327</v>
+        <v>307</v>
       </c>
       <c r="G258" t="n">
         <v>3</v>
@@ -12598,7 +12598,7 @@
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>LAYUP</t>
+          <t>Layup (3H)</t>
         </is>
       </c>
     </row>
@@ -12623,7 +12623,7 @@
         <v>4</v>
       </c>
       <c r="F259" t="n">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="G259" t="n">
         <v>3</v>
@@ -12646,7 +12646,7 @@
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>9I</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -12671,7 +12671,7 @@
         <v>4</v>
       </c>
       <c r="F260" t="n">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="G260" t="n">
         <v>2</v>
@@ -12689,12 +12689,12 @@
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>D</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>SW</t>
         </is>
       </c>
     </row>
@@ -12763,7 +12763,7 @@
         <v>4</v>
       </c>
       <c r="F262" t="n">
-        <v>143</v>
+        <v>109</v>
       </c>
       <c r="G262" t="n">
         <v>2</v>
@@ -12781,12 +12781,12 @@
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>D</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>9I</t>
+          <t>SW</t>
         </is>
       </c>
     </row>
@@ -12811,7 +12811,7 @@
         <v>4</v>
       </c>
       <c r="F263" t="n">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="G263" t="n">
         <v>2</v>
@@ -12834,7 +12834,7 @@
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>9I</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -12877,7 +12877,7 @@
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>9I</t>
         </is>
       </c>
       <c r="L264" t="inlineStr"/>
@@ -12903,7 +12903,7 @@
         <v>4</v>
       </c>
       <c r="F265" t="n">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="G265" t="n">
         <v>2</v>
@@ -12926,7 +12926,7 @@
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>9I</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -12951,7 +12951,7 @@
         <v>5</v>
       </c>
       <c r="F266" t="n">
-        <v>328</v>
+        <v>308</v>
       </c>
       <c r="G266" t="n">
         <v>3</v>
@@ -12974,7 +12974,7 @@
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>LAYUP</t>
+          <t>Layup (3H)</t>
         </is>
       </c>
     </row>
@@ -13043,7 +13043,7 @@
         <v>4</v>
       </c>
       <c r="F268" t="n">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="G268" t="n">
         <v>3</v>
@@ -13066,7 +13066,7 @@
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -13091,7 +13091,7 @@
         <v>4</v>
       </c>
       <c r="F269" t="n">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="G269" t="n">
         <v>2</v>
@@ -13114,7 +13114,7 @@
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>SW</t>
         </is>
       </c>
     </row>
@@ -13139,7 +13139,7 @@
         <v>4</v>
       </c>
       <c r="F270" t="n">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="G270" t="n">
         <v>3</v>
@@ -13162,7 +13162,7 @@
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -13187,7 +13187,7 @@
         <v>4</v>
       </c>
       <c r="F271" t="n">
-        <v>207</v>
+        <v>187</v>
       </c>
       <c r="G271" t="n">
         <v>2</v>
@@ -13210,7 +13210,7 @@
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>5I</t>
         </is>
       </c>
     </row>
@@ -13235,7 +13235,7 @@
         <v>4</v>
       </c>
       <c r="F272" t="n">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="G272" t="n">
         <v>3</v>
@@ -13258,7 +13258,7 @@
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>LW</t>
         </is>
       </c>
     </row>
@@ -13283,7 +13283,7 @@
         <v>4</v>
       </c>
       <c r="F273" t="n">
-        <v>168</v>
+        <v>148</v>
       </c>
       <c r="G273" t="n">
         <v>3</v>
@@ -13306,7 +13306,7 @@
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>9I</t>
         </is>
       </c>
     </row>
@@ -13331,7 +13331,7 @@
         <v>4</v>
       </c>
       <c r="F274" t="n">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="G274" t="n">
         <v>1</v>
@@ -13354,7 +13354,7 @@
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>PW</t>
         </is>
       </c>
     </row>
@@ -13423,7 +13423,7 @@
         <v>4</v>
       </c>
       <c r="F276" t="n">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="G276" t="n">
         <v>1</v>
@@ -13446,7 +13446,7 @@
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>LW</t>
         </is>
       </c>
     </row>
@@ -13471,7 +13471,7 @@
         <v>4</v>
       </c>
       <c r="F277" t="n">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="G277" t="n">
         <v>1</v>
@@ -13494,7 +13494,7 @@
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -13519,7 +13519,7 @@
         <v>4</v>
       </c>
       <c r="F278" t="n">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="G278" t="n">
         <v>1</v>
@@ -13542,7 +13542,7 @@
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>3H</t>
+          <t>7I</t>
         </is>
       </c>
     </row>
@@ -13585,7 +13585,7 @@
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>9I</t>
         </is>
       </c>
       <c r="L279" t="inlineStr"/>
@@ -13611,7 +13611,7 @@
         <v>5</v>
       </c>
       <c r="F280" t="n">
-        <v>267</v>
+        <v>247</v>
       </c>
       <c r="G280" t="n">
         <v>2</v>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>Layup (4I)</t>
+          <t>Layup (3H)</t>
         </is>
       </c>
     </row>
@@ -13659,7 +13659,7 @@
         <v>4</v>
       </c>
       <c r="F281" t="n">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="G281" t="n">
         <v>1</v>
@@ -13682,7 +13682,7 @@
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>LW</t>
         </is>
       </c>
     </row>
@@ -13707,7 +13707,7 @@
         <v>4</v>
       </c>
       <c r="F282" t="n">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="G282" t="n">
         <v>2</v>
@@ -13730,7 +13730,7 @@
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>3H</t>
+          <t>7I</t>
         </is>
       </c>
     </row>
@@ -13799,7 +13799,7 @@
         <v>5</v>
       </c>
       <c r="F284" t="n">
-        <v>272</v>
+        <v>252</v>
       </c>
       <c r="G284" t="n">
         <v>2</v>
@@ -13822,7 +13822,7 @@
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>Layup (4I)</t>
+          <t>Layup (9I)</t>
         </is>
       </c>
     </row>
@@ -13847,7 +13847,7 @@
         <v>4</v>
       </c>
       <c r="F285" t="n">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="G285" t="n">
         <v>2</v>
@@ -13870,7 +13870,7 @@
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>5I</t>
+          <t>8I</t>
         </is>
       </c>
     </row>
@@ -13895,7 +13895,7 @@
         <v>5</v>
       </c>
       <c r="F286" t="n">
-        <v>319</v>
+        <v>299</v>
       </c>
       <c r="G286" t="n">
         <v>2</v>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>LAYUP</t>
+          <t>Layup (3H)</t>
         </is>
       </c>
     </row>
@@ -13943,7 +13943,7 @@
         <v>4</v>
       </c>
       <c r="F287" t="n">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="G287" t="n">
         <v>1</v>
@@ -13966,7 +13966,7 @@
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>9I</t>
         </is>
       </c>
     </row>
@@ -14035,7 +14035,7 @@
         <v>5</v>
       </c>
       <c r="F289" t="n">
-        <v>278</v>
+        <v>258</v>
       </c>
       <c r="G289" t="n">
         <v>1</v>
@@ -14058,7 +14058,7 @@
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t>Layup (6I)</t>
+          <t>Layup (8I)</t>
         </is>
       </c>
     </row>
@@ -14083,7 +14083,7 @@
         <v>4</v>
       </c>
       <c r="F290" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="G290" t="n">
         <v>2</v>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>Layup (4I)</t>
+          <t>6I</t>
         </is>
       </c>
     </row>
@@ -14131,7 +14131,7 @@
         <v>4</v>
       </c>
       <c r="F291" t="n">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="G291" t="n">
         <v>1.67</v>
@@ -14154,7 +14154,7 @@
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>SW</t>
         </is>
       </c>
     </row>
@@ -14197,7 +14197,7 @@
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t>3H</t>
+          <t>5I</t>
         </is>
       </c>
       <c r="L292" t="inlineStr"/>
@@ -14223,7 +14223,7 @@
         <v>5</v>
       </c>
       <c r="F293" t="n">
-        <v>297</v>
+        <v>277</v>
       </c>
       <c r="G293" t="n">
         <v>1.67</v>
@@ -14246,7 +14246,7 @@
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t>Layup (3H)</t>
+          <t>Layup (6I)</t>
         </is>
       </c>
     </row>
@@ -14271,7 +14271,7 @@
         <v>4</v>
       </c>
       <c r="F294" t="n">
-        <v>140</v>
+        <v>106</v>
       </c>
       <c r="G294" t="n">
         <v>1.67</v>
@@ -14289,12 +14289,12 @@
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>D</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>SW</t>
         </is>
       </c>
     </row>
@@ -14337,7 +14337,7 @@
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>9I</t>
         </is>
       </c>
       <c r="L295" t="inlineStr"/>
@@ -14363,7 +14363,7 @@
         <v>4</v>
       </c>
       <c r="F296" t="n">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="G296" t="n">
         <v>2</v>
@@ -14386,7 +14386,7 @@
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>9I</t>
         </is>
       </c>
     </row>
@@ -14411,7 +14411,7 @@
         <v>4</v>
       </c>
       <c r="F297" t="n">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="G297" t="n">
         <v>1.33</v>
@@ -14434,7 +14434,7 @@
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>8I</t>
         </is>
       </c>
     </row>
@@ -14459,7 +14459,7 @@
         <v>5</v>
       </c>
       <c r="F298" t="n">
-        <v>289</v>
+        <v>269</v>
       </c>
       <c r="G298" t="n">
         <v>2</v>
@@ -14482,7 +14482,7 @@
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t>Layup (3H)</t>
+          <t>Layup (7I)</t>
         </is>
       </c>
     </row>
@@ -14507,7 +14507,7 @@
         <v>4</v>
       </c>
       <c r="F299" t="n">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="G299" t="n">
         <v>2</v>
@@ -14525,12 +14525,12 @@
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>D</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>LW</t>
         </is>
       </c>
     </row>
@@ -14555,7 +14555,7 @@
         <v>5</v>
       </c>
       <c r="F300" t="n">
-        <v>274</v>
+        <v>254</v>
       </c>
       <c r="G300" t="n">
         <v>1.33</v>
@@ -14578,7 +14578,7 @@
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t>Layup (4I)</t>
+          <t>Layup (8I)</t>
         </is>
       </c>
     </row>
@@ -14603,7 +14603,7 @@
         <v>4</v>
       </c>
       <c r="F301" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="G301" t="n">
         <v>1.67</v>
@@ -14626,7 +14626,7 @@
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>SW</t>
         </is>
       </c>
     </row>
@@ -14669,7 +14669,7 @@
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t>5I</t>
+          <t>6I</t>
         </is>
       </c>
       <c r="L302" t="inlineStr"/>
@@ -14695,7 +14695,7 @@
         <v>4</v>
       </c>
       <c r="F303" t="n">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="G303" t="n">
         <v>1.33</v>
@@ -14718,7 +14718,7 @@
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>3H</t>
+          <t>7I</t>
         </is>
       </c>
     </row>
@@ -14743,7 +14743,7 @@
         <v>4</v>
       </c>
       <c r="F304" t="n">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="G304" t="n">
         <v>1.67</v>
@@ -14766,7 +14766,7 @@
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>SW</t>
         </is>
       </c>
     </row>
@@ -14809,7 +14809,7 @@
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>8I</t>
         </is>
       </c>
       <c r="L305" t="inlineStr"/>
@@ -14835,7 +14835,7 @@
         <v>4</v>
       </c>
       <c r="F306" t="n">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="G306" t="n">
         <v>2.33</v>
@@ -14858,7 +14858,7 @@
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>3H</t>
+          <t>6I</t>
         </is>
       </c>
     </row>
@@ -14883,7 +14883,7 @@
         <v>5</v>
       </c>
       <c r="F307" t="n">
-        <v>326</v>
+        <v>306</v>
       </c>
       <c r="G307" t="n">
         <v>1.67</v>
@@ -14906,7 +14906,7 @@
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>LAYUP</t>
+          <t>Layup (3H)</t>
         </is>
       </c>
     </row>
@@ -14931,7 +14931,7 @@
         <v>4</v>
       </c>
       <c r="F308" t="n">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="G308" t="n">
         <v>2</v>
@@ -14954,7 +14954,7 @@
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -14979,7 +14979,7 @@
         <v>5</v>
       </c>
       <c r="F309" t="n">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="G309" t="n">
         <v>3</v>
@@ -15002,7 +15002,7 @@
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>Layup (4I)</t>
+          <t>Layup (3H)</t>
         </is>
       </c>
     </row>
@@ -15045,7 +15045,7 @@
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>6I</t>
         </is>
       </c>
       <c r="L310" t="inlineStr"/>
@@ -15071,7 +15071,7 @@
         <v>4</v>
       </c>
       <c r="F311" t="n">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="G311" t="n">
         <v>2</v>
@@ -15094,7 +15094,7 @@
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>SW</t>
         </is>
       </c>
     </row>
@@ -15119,7 +15119,7 @@
         <v>4</v>
       </c>
       <c r="F312" t="n">
-        <v>143</v>
+        <v>109</v>
       </c>
       <c r="G312" t="n">
         <v>2</v>
@@ -15137,12 +15137,12 @@
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>D</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>9I</t>
+          <t>SW</t>
         </is>
       </c>
     </row>
@@ -15167,7 +15167,7 @@
         <v>4</v>
       </c>
       <c r="F313" t="n">
-        <v>215</v>
+        <v>195</v>
       </c>
       <c r="G313" t="n">
         <v>2</v>
@@ -15190,7 +15190,7 @@
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>3H</t>
         </is>
       </c>
     </row>
@@ -15215,7 +15215,7 @@
         <v>4</v>
       </c>
       <c r="F314" t="n">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="G314" t="n">
         <v>1</v>
@@ -15238,7 +15238,7 @@
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>PW</t>
         </is>
       </c>
     </row>
@@ -15307,7 +15307,7 @@
         <v>5</v>
       </c>
       <c r="F316" t="n">
-        <v>273</v>
+        <v>253</v>
       </c>
       <c r="G316" t="n">
         <v>2</v>
@@ -15330,7 +15330,7 @@
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t>Layup (4I)</t>
+          <t>Layup (9I)</t>
         </is>
       </c>
     </row>
@@ -15355,7 +15355,7 @@
         <v>4</v>
       </c>
       <c r="F317" t="n">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="G317" t="n">
         <v>2</v>
@@ -15378,7 +15378,7 @@
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t>9I</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -15403,7 +15403,7 @@
         <v>5</v>
       </c>
       <c r="F318" t="n">
-        <v>348</v>
+        <v>328</v>
       </c>
       <c r="G318" t="n">
         <v>1</v>
@@ -15426,7 +15426,7 @@
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t>LAYUP</t>
+          <t>Layup (3W)</t>
         </is>
       </c>
     </row>
@@ -15451,7 +15451,7 @@
         <v>4</v>
       </c>
       <c r="F319" t="n">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="G319" t="n">
         <v>2</v>
@@ -15474,7 +15474,7 @@
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t>9I</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -15543,7 +15543,7 @@
         <v>4</v>
       </c>
       <c r="F321" t="n">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="G321" t="n">
         <v>2</v>
@@ -15566,7 +15566,7 @@
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t>9I</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -15591,7 +15591,7 @@
         <v>4</v>
       </c>
       <c r="F322" t="n">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="G322" t="n">
         <v>1</v>
@@ -15614,7 +15614,7 @@
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>9I</t>
         </is>
       </c>
     </row>
@@ -15657,7 +15657,7 @@
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>9I</t>
         </is>
       </c>
       <c r="L323" t="inlineStr"/>
@@ -15683,7 +15683,7 @@
         <v>4</v>
       </c>
       <c r="F324" t="n">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="G324" t="n">
         <v>2</v>
@@ -15731,7 +15731,7 @@
         <v>5</v>
       </c>
       <c r="F325" t="n">
-        <v>308</v>
+        <v>288</v>
       </c>
       <c r="G325" t="n">
         <v>2</v>
@@ -15754,7 +15754,7 @@
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t>Layup (3W)</t>
+          <t>Layup (3H)</t>
         </is>
       </c>
     </row>
@@ -15779,7 +15779,7 @@
         <v>4</v>
       </c>
       <c r="F326" t="n">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="G326" t="n">
         <v>2</v>
@@ -15802,7 +15802,7 @@
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t>6I</t>
+          <t>8I</t>
         </is>
       </c>
     </row>
@@ -15827,7 +15827,7 @@
         <v>5</v>
       </c>
       <c r="F327" t="n">
-        <v>277</v>
+        <v>257</v>
       </c>
       <c r="G327" t="n">
         <v>3</v>
@@ -15850,7 +15850,7 @@
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t>Layup (6I)</t>
+          <t>Layup (8I)</t>
         </is>
       </c>
     </row>
@@ -15893,7 +15893,7 @@
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>6I</t>
         </is>
       </c>
       <c r="L328" t="inlineStr"/>
@@ -15919,7 +15919,7 @@
         <v>4</v>
       </c>
       <c r="F329" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="G329" t="n">
         <v>2</v>
@@ -15942,7 +15942,7 @@
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>9I</t>
         </is>
       </c>
     </row>
@@ -15967,7 +15967,7 @@
         <v>4</v>
       </c>
       <c r="F330" t="n">
-        <v>205</v>
+        <v>185</v>
       </c>
       <c r="G330" t="n">
         <v>1</v>
@@ -15990,7 +15990,7 @@
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>5I</t>
         </is>
       </c>
     </row>
@@ -16015,7 +16015,7 @@
         <v>4</v>
       </c>
       <c r="F331" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="G331" t="n">
         <v>2</v>
@@ -16063,7 +16063,7 @@
         <v>5</v>
       </c>
       <c r="F332" t="n">
-        <v>344</v>
+        <v>324</v>
       </c>
       <c r="G332" t="n">
         <v>1</v>
@@ -16086,7 +16086,7 @@
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t>LAYUP</t>
+          <t>Layup (3W)</t>
         </is>
       </c>
     </row>
@@ -16155,7 +16155,7 @@
         <v>4</v>
       </c>
       <c r="F334" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="G334" t="n">
         <v>2</v>
@@ -16178,7 +16178,7 @@
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>SW</t>
         </is>
       </c>
     </row>
@@ -16203,7 +16203,7 @@
         <v>4</v>
       </c>
       <c r="F335" t="n">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="G335" t="n">
         <v>2</v>
@@ -16226,7 +16226,7 @@
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>8I</t>
         </is>
       </c>
     </row>
@@ -16269,7 +16269,7 @@
       </c>
       <c r="K336" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>8I</t>
         </is>
       </c>
       <c r="L336" t="inlineStr"/>
@@ -16295,7 +16295,7 @@
         <v>4</v>
       </c>
       <c r="F337" t="n">
-        <v>247</v>
+        <v>227</v>
       </c>
       <c r="G337" t="n">
         <v>2</v>
@@ -16318,7 +16318,7 @@
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t>Layup (3H)</t>
+          <t>3W</t>
         </is>
       </c>
     </row>
@@ -16343,7 +16343,7 @@
         <v>5</v>
       </c>
       <c r="F338" t="n">
-        <v>291</v>
+        <v>271</v>
       </c>
       <c r="G338" t="n">
         <v>1</v>
@@ -16366,7 +16366,7 @@
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t>Layup (3H)</t>
+          <t>Layup (7I)</t>
         </is>
       </c>
     </row>
@@ -16391,7 +16391,7 @@
         <v>4</v>
       </c>
       <c r="F339" t="n">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="G339" t="n">
         <v>1</v>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t>3H</t>
+          <t>6I</t>
         </is>
       </c>
     </row>
@@ -16439,7 +16439,7 @@
         <v>5</v>
       </c>
       <c r="F340" t="n">
-        <v>284</v>
+        <v>264</v>
       </c>
       <c r="G340" t="n">
         <v>1</v>
@@ -16462,7 +16462,7 @@
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t>Layup (3H)</t>
+          <t>Layup (8I)</t>
         </is>
       </c>
     </row>
@@ -16505,7 +16505,7 @@
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t>5I</t>
+          <t>6I</t>
         </is>
       </c>
       <c r="L341" t="inlineStr"/>
@@ -16531,7 +16531,7 @@
         <v>4</v>
       </c>
       <c r="F342" t="n">
-        <v>139</v>
+        <v>105</v>
       </c>
       <c r="G342" t="n">
         <v>2</v>
@@ -16549,12 +16549,12 @@
       </c>
       <c r="K342" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>D</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>SW</t>
         </is>
       </c>
     </row>
@@ -16579,7 +16579,7 @@
         <v>4</v>
       </c>
       <c r="F343" t="n">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="G343" t="n">
         <v>1</v>
@@ -16602,7 +16602,7 @@
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t>3H</t>
+          <t>7I</t>
         </is>
       </c>
     </row>
@@ -16627,7 +16627,7 @@
         <v>4</v>
       </c>
       <c r="F344" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="G344" t="n">
         <v>1.75</v>
@@ -16719,7 +16719,7 @@
         <v>4</v>
       </c>
       <c r="F346" t="n">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="G346" t="n">
         <v>2</v>
@@ -16737,12 +16737,12 @@
       </c>
       <c r="K346" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>D</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>SW</t>
         </is>
       </c>
     </row>
@@ -16785,7 +16785,7 @@
       </c>
       <c r="K347" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>6I</t>
         </is>
       </c>
       <c r="L347" t="inlineStr"/>
@@ -16811,7 +16811,7 @@
         <v>5</v>
       </c>
       <c r="F348" t="n">
-        <v>234</v>
+        <v>214</v>
       </c>
       <c r="G348" t="n">
         <v>2.25</v>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t>Layup (3H)</t>
+          <t>3W</t>
         </is>
       </c>
     </row>
@@ -16859,7 +16859,7 @@
         <v>4</v>
       </c>
       <c r="F349" t="n">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="G349" t="n">
         <v>2</v>
@@ -16882,7 +16882,7 @@
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>9I</t>
         </is>
       </c>
     </row>
@@ -16907,7 +16907,7 @@
         <v>4</v>
       </c>
       <c r="F350" t="n">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="G350" t="n">
         <v>2</v>
@@ -16925,12 +16925,12 @@
       </c>
       <c r="K350" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>D</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>LW</t>
         </is>
       </c>
     </row>
@@ -16955,7 +16955,7 @@
         <v>4</v>
       </c>
       <c r="F351" t="n">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="G351" t="n">
         <v>2.25</v>
@@ -16978,7 +16978,7 @@
       </c>
       <c r="L351" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -17003,7 +17003,7 @@
         <v>5</v>
       </c>
       <c r="F352" t="n">
-        <v>311</v>
+        <v>291</v>
       </c>
       <c r="G352" t="n">
         <v>2</v>
@@ -17026,7 +17026,7 @@
       </c>
       <c r="L352" t="inlineStr">
         <is>
-          <t>Layup (3W)</t>
+          <t>Layup (3H)</t>
         </is>
       </c>
     </row>
@@ -17051,7 +17051,7 @@
         <v>4</v>
       </c>
       <c r="F353" t="n">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="G353" t="n">
         <v>2.25</v>
@@ -17074,7 +17074,7 @@
       </c>
       <c r="L353" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>SW</t>
         </is>
       </c>
     </row>
@@ -17117,7 +17117,7 @@
       </c>
       <c r="K354" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>8I</t>
         </is>
       </c>
       <c r="L354" t="inlineStr"/>
@@ -17143,7 +17143,7 @@
         <v>4</v>
       </c>
       <c r="F355" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="G355" t="n">
         <v>1.75</v>
@@ -17166,7 +17166,7 @@
       </c>
       <c r="L355" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -17191,7 +17191,7 @@
         <v>5</v>
       </c>
       <c r="F356" t="n">
-        <v>332</v>
+        <v>312</v>
       </c>
       <c r="G356" t="n">
         <v>2</v>
@@ -17214,7 +17214,7 @@
       </c>
       <c r="L356" t="inlineStr">
         <is>
-          <t>LAYUP</t>
+          <t>Layup (3H)</t>
         </is>
       </c>
     </row>
@@ -17257,7 +17257,7 @@
       </c>
       <c r="K357" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>7I</t>
         </is>
       </c>
       <c r="L357" t="inlineStr"/>
@@ -17283,7 +17283,7 @@
         <v>5</v>
       </c>
       <c r="F358" t="n">
-        <v>304</v>
+        <v>284</v>
       </c>
       <c r="G358" t="n">
         <v>2</v>
@@ -17306,7 +17306,7 @@
       </c>
       <c r="L358" t="inlineStr">
         <is>
-          <t>Layup (3W)</t>
+          <t>Layup (5I)</t>
         </is>
       </c>
     </row>
@@ -17375,7 +17375,7 @@
         <v>4</v>
       </c>
       <c r="F360" t="n">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="G360" t="n">
         <v>2.5</v>
@@ -17398,7 +17398,7 @@
       </c>
       <c r="L360" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>9I</t>
         </is>
       </c>
     </row>
@@ -17423,7 +17423,7 @@
         <v>4</v>
       </c>
       <c r="F361" t="n">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="G361" t="n">
         <v>2.25</v>
@@ -17446,7 +17446,7 @@
       </c>
       <c r="L361" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>PW</t>
         </is>
       </c>
     </row>
@@ -17471,7 +17471,7 @@
         <v>4</v>
       </c>
       <c r="F362" t="n">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="G362" t="n">
         <v>2</v>
@@ -17494,7 +17494,7 @@
       </c>
       <c r="L362" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -17519,7 +17519,7 @@
         <v>5</v>
       </c>
       <c r="F363" t="n">
-        <v>257</v>
+        <v>237</v>
       </c>
       <c r="G363" t="n">
         <v>3</v>
@@ -17542,7 +17542,7 @@
       </c>
       <c r="L363" t="inlineStr">
         <is>
-          <t>Layup (4I)</t>
+          <t>Layup (5I)</t>
         </is>
       </c>
     </row>
@@ -17567,7 +17567,7 @@
         <v>4</v>
       </c>
       <c r="F364" t="n">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="G364" t="n">
         <v>1</v>
@@ -17590,7 +17590,7 @@
       </c>
       <c r="L364" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>LW</t>
         </is>
       </c>
     </row>
@@ -17615,7 +17615,7 @@
         <v>4</v>
       </c>
       <c r="F365" t="n">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="G365" t="n">
         <v>2</v>
@@ -17638,7 +17638,7 @@
       </c>
       <c r="L365" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>PW</t>
         </is>
       </c>
     </row>
@@ -17663,7 +17663,7 @@
         <v>5</v>
       </c>
       <c r="F366" t="n">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="G366" t="n">
         <v>2</v>
@@ -17686,7 +17686,7 @@
       </c>
       <c r="L366" t="inlineStr">
         <is>
-          <t>Layup (4I)</t>
+          <t>Layup (5I)</t>
         </is>
       </c>
     </row>
@@ -17755,7 +17755,7 @@
         <v>4</v>
       </c>
       <c r="F368" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="G368" t="n">
         <v>2</v>
@@ -17778,7 +17778,7 @@
       </c>
       <c r="L368" t="inlineStr">
         <is>
-          <t>3H</t>
+          <t>7I</t>
         </is>
       </c>
     </row>
@@ -17821,7 +17821,7 @@
       </c>
       <c r="K369" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>7I</t>
         </is>
       </c>
       <c r="L369" t="inlineStr"/>
@@ -17847,7 +17847,7 @@
         <v>4</v>
       </c>
       <c r="F370" t="n">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="G370" t="n">
         <v>1</v>
@@ -17870,7 +17870,7 @@
       </c>
       <c r="L370" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>9I</t>
         </is>
       </c>
     </row>
@@ -17895,7 +17895,7 @@
         <v>5</v>
       </c>
       <c r="F371" t="n">
-        <v>247</v>
+        <v>227</v>
       </c>
       <c r="G371" t="n">
         <v>2</v>
@@ -17918,7 +17918,7 @@
       </c>
       <c r="L371" t="inlineStr">
         <is>
-          <t>Layup (3H)</t>
+          <t>3W</t>
         </is>
       </c>
     </row>
@@ -17943,7 +17943,7 @@
         <v>4</v>
       </c>
       <c r="F372" t="n">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="G372" t="n">
         <v>1</v>
@@ -17961,12 +17961,12 @@
       </c>
       <c r="K372" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>D</t>
         </is>
       </c>
       <c r="L372" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>LW</t>
         </is>
       </c>
     </row>
@@ -18035,7 +18035,7 @@
         <v>4</v>
       </c>
       <c r="F374" t="n">
-        <v>154</v>
+        <v>134</v>
       </c>
       <c r="G374" t="n">
         <v>2</v>
@@ -18058,7 +18058,7 @@
       </c>
       <c r="L374" t="inlineStr">
         <is>
-          <t>4I</t>
+          <t>PW</t>
         </is>
       </c>
     </row>
@@ -18127,7 +18127,7 @@
         <v>5</v>
       </c>
       <c r="F376" t="n">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="G376" t="n">
         <v>2</v>
@@ -18150,7 +18150,7 @@
       </c>
       <c r="L376" t="inlineStr">
         <is>
-          <t>LAYUP</t>
+          <t>Layup (3H)</t>
         </is>
       </c>
     </row>
@@ -18175,7 +18175,7 @@
         <v>4</v>
       </c>
       <c r="F377" t="n">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="G377" t="n">
         <v>2</v>
@@ -18198,7 +18198,7 @@
       </c>
       <c r="L377" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>LW</t>
         </is>
       </c>
     </row>
@@ -18223,7 +18223,7 @@
         <v>4</v>
       </c>
       <c r="F378" t="n">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="G378" t="n">
         <v>2</v>
@@ -18246,7 +18246,7 @@
       </c>
       <c r="L378" t="inlineStr">
         <is>
-          <t>3H</t>
+          <t>6I</t>
         </is>
       </c>
     </row>
@@ -18271,7 +18271,7 @@
         <v>4</v>
       </c>
       <c r="F379" t="n">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="G379" t="n">
         <v>2</v>
@@ -18289,12 +18289,12 @@
       </c>
       <c r="K379" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>D</t>
         </is>
       </c>
       <c r="L379" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>LW</t>
         </is>
       </c>
     </row>

--- a/golf_recommendations.xlsx
+++ b/golf_recommendations.xlsx
@@ -818,7 +818,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Layup (6I)</t>
+          <t>Layup (5I)</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>9I</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>3H</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>PW</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Layup (9I)</t>
+          <t>LAYUP</t>
         </is>
       </c>
     </row>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Layup (6I)</t>
+          <t>3W</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>9I</t>
         </is>
       </c>
     </row>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>8I</t>
+          <t>7I</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
@@ -3030,7 +3030,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
         <v>4</v>
       </c>
       <c r="F57" t="n">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="G57" t="n">
         <v>1.75</v>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>3W</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>PW</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>PW</t>
         </is>
       </c>
     </row>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>9I</t>
+          <t>8I</t>
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
@@ -3383,7 +3383,7 @@
         <v>4</v>
       </c>
       <c r="F63" t="n">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="G63" t="n">
         <v>2</v>
@@ -3401,12 +3401,12 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>3W</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>PW</t>
         </is>
       </c>
     </row>
@@ -3638,7 +3638,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Layup (8I)</t>
+          <t>Layup (7I)</t>
         </is>
       </c>
     </row>
@@ -3734,7 +3734,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>8I</t>
+          <t>7I</t>
         </is>
       </c>
       <c r="L85" t="inlineStr"/>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>8I</t>
+          <t>7I</t>
         </is>
       </c>
     </row>
@@ -5014,7 +5014,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>PW</t>
         </is>
       </c>
     </row>
@@ -5246,7 +5246,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -5950,7 +5950,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>9I</t>
         </is>
       </c>
     </row>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>8I</t>
+          <t>7I</t>
         </is>
       </c>
       <c r="L124" t="inlineStr"/>
@@ -6325,7 +6325,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>9I</t>
+          <t>8I</t>
         </is>
       </c>
       <c r="L125" t="inlineStr"/>
@@ -6447,7 +6447,7 @@
         <v>4</v>
       </c>
       <c r="F128" t="n">
-        <v>150</v>
+        <v>177</v>
       </c>
       <c r="G128" t="n">
         <v>2.6</v>
@@ -6465,12 +6465,12 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>3W</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>9I</t>
+          <t>6I</t>
         </is>
       </c>
     </row>
@@ -6797,7 +6797,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>9I</t>
+          <t>8I</t>
         </is>
       </c>
       <c r="L135" t="inlineStr"/>
@@ -6846,7 +6846,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>Layup (6I)</t>
+          <t>3W</t>
         </is>
       </c>
     </row>
@@ -7077,7 +7077,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>8I</t>
+          <t>7I</t>
         </is>
       </c>
       <c r="L141" t="inlineStr"/>
@@ -7409,7 +7409,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>3H</t>
+          <t>5I</t>
         </is>
       </c>
       <c r="L148" t="inlineStr"/>
@@ -7689,7 +7689,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>3H</t>
+          <t>5I</t>
         </is>
       </c>
       <c r="L154" t="inlineStr"/>
@@ -8022,7 +8022,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>Layup (6I)</t>
+          <t>Layup (5I)</t>
         </is>
       </c>
     </row>
@@ -8118,7 +8118,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>PW</t>
         </is>
       </c>
     </row>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>PW</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>PW</t>
         </is>
       </c>
     </row>
@@ -9987,7 +9987,7 @@
         <v>4</v>
       </c>
       <c r="F203" t="n">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="G203" t="n">
         <v>2</v>
@@ -10005,12 +10005,12 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>3W</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>PW</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -10150,7 +10150,7 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>8I</t>
+          <t>7I</t>
         </is>
       </c>
     </row>
@@ -10193,7 +10193,7 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>9I</t>
+          <t>LAYUP (SW)</t>
         </is>
       </c>
       <c r="L207" t="inlineStr"/>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>6I</t>
+          <t>5I</t>
         </is>
       </c>
     </row>
@@ -10666,7 +10666,7 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>Layup (6I)</t>
+          <t>Layup (5I)</t>
         </is>
       </c>
     </row>
@@ -12011,7 +12011,7 @@
         <v>4</v>
       </c>
       <c r="F246" t="n">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="G246" t="n">
         <v>2.5</v>
@@ -12029,12 +12029,12 @@
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>3W</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>PW</t>
         </is>
       </c>
     </row>
@@ -12646,7 +12646,7 @@
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>PW</t>
         </is>
       </c>
     </row>
@@ -12786,7 +12786,7 @@
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -12834,7 +12834,7 @@
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>PW</t>
         </is>
       </c>
     </row>
@@ -12877,7 +12877,7 @@
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t>9I</t>
+          <t>8I</t>
         </is>
       </c>
       <c r="L264" t="inlineStr"/>
@@ -12926,7 +12926,7 @@
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>PW</t>
         </is>
       </c>
     </row>
@@ -13354,7 +13354,7 @@
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>9I</t>
         </is>
       </c>
     </row>
@@ -13397,7 +13397,7 @@
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t>3H</t>
+          <t>5I</t>
         </is>
       </c>
       <c r="L275" t="inlineStr"/>
@@ -13585,7 +13585,7 @@
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t>9I</t>
+          <t>LAYUP (SW)</t>
         </is>
       </c>
       <c r="L279" t="inlineStr"/>
@@ -13822,7 +13822,7 @@
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>Layup (9I)</t>
+          <t>Layup (8I)</t>
         </is>
       </c>
     </row>
@@ -14294,7 +14294,7 @@
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -14337,7 +14337,7 @@
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t>9I</t>
+          <t>8I</t>
         </is>
       </c>
       <c r="L295" t="inlineStr"/>
@@ -14386,7 +14386,7 @@
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t>9I</t>
+          <t>8I</t>
         </is>
       </c>
     </row>
@@ -14743,7 +14743,7 @@
         <v>4</v>
       </c>
       <c r="F304" t="n">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="G304" t="n">
         <v>1.67</v>
@@ -14761,12 +14761,12 @@
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>3W</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>PW</t>
         </is>
       </c>
     </row>
@@ -15071,7 +15071,7 @@
         <v>4</v>
       </c>
       <c r="F311" t="n">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="G311" t="n">
         <v>2</v>
@@ -15089,12 +15089,12 @@
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>3W</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>PW</t>
         </is>
       </c>
     </row>
@@ -15142,7 +15142,7 @@
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -15330,7 +15330,7 @@
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t>Layup (9I)</t>
+          <t>Layup (8I)</t>
         </is>
       </c>
     </row>
@@ -15378,7 +15378,7 @@
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>PW</t>
         </is>
       </c>
     </row>
@@ -15474,7 +15474,7 @@
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>PW</t>
         </is>
       </c>
     </row>
@@ -15566,7 +15566,7 @@
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>PW</t>
         </is>
       </c>
     </row>
@@ -15614,7 +15614,7 @@
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t>9I</t>
+          <t>8I</t>
         </is>
       </c>
     </row>
@@ -15657,7 +15657,7 @@
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t>9I</t>
+          <t>LAYUP (SW)</t>
         </is>
       </c>
       <c r="L323" t="inlineStr"/>
@@ -15919,7 +15919,7 @@
         <v>4</v>
       </c>
       <c r="F329" t="n">
-        <v>150</v>
+        <v>177</v>
       </c>
       <c r="G329" t="n">
         <v>2</v>
@@ -15937,12 +15937,12 @@
       </c>
       <c r="K329" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>3W</t>
         </is>
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t>9I</t>
+          <t>6I</t>
         </is>
       </c>
     </row>
@@ -16129,7 +16129,7 @@
       </c>
       <c r="K333" t="inlineStr">
         <is>
-          <t>3H</t>
+          <t>5I</t>
         </is>
       </c>
       <c r="L333" t="inlineStr"/>
@@ -16462,7 +16462,7 @@
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t>Layup (8I)</t>
+          <t>Layup (7I)</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>3H</t>
         </is>
       </c>
     </row>
@@ -17398,7 +17398,7 @@
       </c>
       <c r="L360" t="inlineStr">
         <is>
-          <t>9I</t>
+          <t>8I</t>
         </is>
       </c>
     </row>
@@ -17446,7 +17446,7 @@
       </c>
       <c r="L361" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>9I</t>
         </is>
       </c>
     </row>

--- a/golf_recommendations.xlsx
+++ b/golf_recommendations.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L433"/>
+  <dimension ref="A1:L451"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,7 +674,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>3H</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Layup (3W)</t>
+          <t>Layup (3H)</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>LAYUP</t>
+          <t>Layup (8I)</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
         <v>4</v>
       </c>
       <c r="F57" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="G57" t="n">
         <v>1.89</v>
@@ -3383,7 +3383,7 @@
         <v>4</v>
       </c>
       <c r="F63" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G63" t="n">
         <v>2</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Layup (3W)</t>
+          <t>Layup (3H)</t>
         </is>
       </c>
     </row>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>LW</t>
         </is>
       </c>
     </row>
@@ -4135,7 +4135,7 @@
         <v>4</v>
       </c>
       <c r="F79" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G79" t="n">
         <v>1.89</v>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>3H</t>
         </is>
       </c>
     </row>
@@ -4966,7 +4966,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>9I</t>
         </is>
       </c>
     </row>
@@ -5670,7 +5670,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>6I</t>
+          <t>7I</t>
         </is>
       </c>
     </row>
@@ -6447,7 +6447,7 @@
         <v>4</v>
       </c>
       <c r="F128" t="n">
-        <v>177</v>
+        <v>150</v>
       </c>
       <c r="G128" t="n">
         <v>2.67</v>
@@ -6465,12 +6465,12 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>D</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>6I</t>
+          <t>8I</t>
         </is>
       </c>
     </row>
@@ -7453,7 +7453,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>6I</t>
+          <t>7I</t>
         </is>
       </c>
       <c r="L149" t="inlineStr"/>
@@ -8022,7 +8022,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>Layup (5I)</t>
+          <t>3W</t>
         </is>
       </c>
     </row>
@@ -8847,7 +8847,7 @@
         <v>4</v>
       </c>
       <c r="F179" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G179" t="n">
         <v>1.33</v>
@@ -9135,7 +9135,7 @@
         <v>4</v>
       </c>
       <c r="F185" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G185" t="n">
         <v>1.33</v>
@@ -9559,7 +9559,7 @@
         <v>4</v>
       </c>
       <c r="F194" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G194" t="n">
         <v>1.2</v>
@@ -9607,7 +9607,7 @@
         <v>4</v>
       </c>
       <c r="F195" t="n">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="G195" t="n">
         <v>2</v>
@@ -9625,12 +9625,12 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>D</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>LW</t>
+          <t>LAYUP</t>
         </is>
       </c>
     </row>
@@ -9987,7 +9987,7 @@
         <v>4</v>
       </c>
       <c r="F203" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="G203" t="n">
         <v>2</v>
@@ -10193,7 +10193,7 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>LAYUP (SW)</t>
+          <t>8I</t>
         </is>
       </c>
       <c r="L207" t="inlineStr"/>
@@ -10526,7 +10526,7 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>Layup (3W)</t>
+          <t>Layup (3H)</t>
         </is>
       </c>
     </row>
@@ -11465,7 +11465,7 @@
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>9I</t>
         </is>
       </c>
       <c r="L234" t="inlineStr"/>
@@ -12026,7 +12026,7 @@
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>9I</t>
         </is>
       </c>
     </row>
@@ -12429,7 +12429,7 @@
         <v>4</v>
       </c>
       <c r="F257" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="G257" t="n">
         <v>2.5</v>
@@ -12878,7 +12878,7 @@
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>8I</t>
+          <t>7I</t>
         </is>
       </c>
     </row>
@@ -12959,7 +12959,7 @@
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>9I</t>
         </is>
       </c>
       <c r="L269" t="inlineStr"/>
@@ -13046,7 +13046,7 @@
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>8I</t>
+          <t>7I</t>
         </is>
       </c>
     </row>
@@ -13378,7 +13378,7 @@
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>LW</t>
         </is>
       </c>
     </row>
@@ -14269,7 +14269,7 @@
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t>LAYUP (SW)</t>
+          <t>8I</t>
         </is>
       </c>
       <c r="L297" t="inlineStr"/>
@@ -14554,7 +14554,7 @@
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>8I</t>
+          <t>7I</t>
         </is>
       </c>
     </row>
@@ -14801,30 +14801,30 @@
         </is>
       </c>
       <c r="B309" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>White</t>
         </is>
       </c>
       <c r="D309" t="n">
-        <v>338</v>
+        <v>394</v>
       </c>
       <c r="E309" t="n">
         <v>4</v>
       </c>
       <c r="F309" t="n">
-        <v>95</v>
+        <v>151</v>
       </c>
       <c r="G309" t="n">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="H309" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="I309" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="J309" t="inlineStr">
         <is>
@@ -14838,7 +14838,7 @@
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>8I</t>
         </is>
       </c>
     </row>
@@ -14849,7 +14849,7 @@
         </is>
       </c>
       <c r="B310" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -14857,34 +14857,38 @@
         </is>
       </c>
       <c r="D310" t="n">
-        <v>187</v>
+        <v>338</v>
       </c>
       <c r="E310" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F310" t="n">
-        <v>187</v>
+        <v>95</v>
       </c>
       <c r="G310" t="n">
         <v>1.83</v>
       </c>
       <c r="H310" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="I310" t="n">
         <v>0.17</v>
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>Focus on Tee Shot (Change Strategy)</t>
+          <t>Work on Tee Shot (Change Strategy)</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t>5I</t>
-        </is>
-      </c>
-      <c r="L310" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -14893,34 +14897,34 @@
         </is>
       </c>
       <c r="B311" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>White</t>
         </is>
       </c>
       <c r="D311" t="n">
-        <v>520</v>
+        <v>314</v>
       </c>
       <c r="E311" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F311" t="n">
-        <v>277</v>
+        <v>71</v>
       </c>
       <c r="G311" t="n">
         <v>2</v>
       </c>
       <c r="H311" t="n">
+        <v>0</v>
+      </c>
+      <c r="I311" t="n">
         <v>0.5</v>
       </c>
-      <c r="I311" t="n">
-        <v>0.17</v>
-      </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>Focus on Approach (Change Strategy)</t>
+          <t>Work on Tee Shot (Change Strategy)</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
@@ -14930,7 +14934,7 @@
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>Layup (6I)</t>
+          <t>LW</t>
         </is>
       </c>
     </row>
@@ -14941,7 +14945,7 @@
         </is>
       </c>
       <c r="B312" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
@@ -14949,38 +14953,34 @@
         </is>
       </c>
       <c r="D312" t="n">
-        <v>349</v>
+        <v>187</v>
       </c>
       <c r="E312" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F312" t="n">
-        <v>106</v>
+        <v>187</v>
       </c>
       <c r="G312" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="H312" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I312" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>Focus on Approach (Change Strategy)</t>
+          <t>Focus on Tee Shot (Change Strategy)</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="L312" t="inlineStr">
-        <is>
-          <t>GW</t>
-        </is>
-      </c>
+          <t>5I</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -14989,34 +14989,34 @@
         </is>
       </c>
       <c r="B313" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>White</t>
         </is>
       </c>
       <c r="D313" t="n">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="E313" t="n">
         <v>3</v>
       </c>
       <c r="F313" t="n">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="G313" t="n">
-        <v>1.67</v>
+        <v>2.5</v>
       </c>
       <c r="H313" t="n">
         <v>0</v>
       </c>
       <c r="I313" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>No Issue</t>
+          <t>Focus on Tee Shot (Change Strategy)</t>
         </is>
       </c>
       <c r="K313" t="inlineStr">
@@ -15033,7 +15033,7 @@
         </is>
       </c>
       <c r="B314" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -15041,22 +15041,22 @@
         </is>
       </c>
       <c r="D314" t="n">
-        <v>394</v>
+        <v>520</v>
       </c>
       <c r="E314" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F314" t="n">
-        <v>151</v>
+        <v>277</v>
       </c>
       <c r="G314" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="H314" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="I314" t="n">
-        <v>0.33</v>
+        <v>0.17</v>
       </c>
       <c r="J314" t="inlineStr">
         <is>
@@ -15070,7 +15070,7 @@
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>8I</t>
+          <t>Layup (6I)</t>
         </is>
       </c>
     </row>
@@ -15081,30 +15081,30 @@
         </is>
       </c>
       <c r="B315" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>White</t>
         </is>
       </c>
       <c r="D315" t="n">
-        <v>399</v>
+        <v>481</v>
       </c>
       <c r="E315" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F315" t="n">
-        <v>156</v>
+        <v>238</v>
       </c>
       <c r="G315" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="H315" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="I315" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="J315" t="inlineStr">
         <is>
@@ -15118,7 +15118,7 @@
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t>8I</t>
+          <t>Layup (5I)</t>
         </is>
       </c>
     </row>
@@ -15129,7 +15129,7 @@
         </is>
       </c>
       <c r="B316" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
@@ -15137,26 +15137,26 @@
         </is>
       </c>
       <c r="D316" t="n">
-        <v>512</v>
+        <v>349</v>
       </c>
       <c r="E316" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F316" t="n">
-        <v>269</v>
+        <v>106</v>
       </c>
       <c r="G316" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="H316" t="n">
         <v>0.5</v>
       </c>
       <c r="I316" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>No Issue</t>
+          <t>Focus on Approach (Change Strategy)</t>
         </is>
       </c>
       <c r="K316" t="inlineStr">
@@ -15166,7 +15166,7 @@
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t>Layup (7I)</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -15177,24 +15177,24 @@
         </is>
       </c>
       <c r="B317" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>White</t>
         </is>
       </c>
       <c r="D317" t="n">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E317" t="n">
         <v>4</v>
       </c>
       <c r="F317" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G317" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="H317" t="n">
         <v>0.5</v>
@@ -15204,7 +15204,7 @@
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>No Issue</t>
+          <t>Focus on Approach (Change Strategy)</t>
         </is>
       </c>
       <c r="K317" t="inlineStr">
@@ -15225,7 +15225,7 @@
         </is>
       </c>
       <c r="B318" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
@@ -15233,23 +15233,23 @@
         </is>
       </c>
       <c r="D318" t="n">
-        <v>497</v>
+        <v>153</v>
       </c>
       <c r="E318" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F318" t="n">
-        <v>254</v>
+        <v>153</v>
       </c>
       <c r="G318" t="n">
         <v>1.67</v>
       </c>
       <c r="H318" t="n">
+        <v>0</v>
+      </c>
+      <c r="I318" t="n">
         <v>0.5</v>
       </c>
-      <c r="I318" t="n">
-        <v>0.33</v>
-      </c>
       <c r="J318" t="inlineStr">
         <is>
           <t>No Issue</t>
@@ -15257,14 +15257,10 @@
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="L318" t="inlineStr">
-        <is>
-          <t>Layup (8I)</t>
-        </is>
-      </c>
+          <t>8I</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -15273,46 +15269,42 @@
         </is>
       </c>
       <c r="B319" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>White</t>
         </is>
       </c>
       <c r="D319" t="n">
-        <v>343</v>
+        <v>128</v>
       </c>
       <c r="E319" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F319" t="n">
-        <v>100</v>
+        <v>128</v>
       </c>
       <c r="G319" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="H319" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="I319" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>Focus on Approach (Change Strategy)</t>
+          <t>No Issue</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="L319" t="inlineStr">
-        <is>
-          <t>SW</t>
-        </is>
-      </c>
+          <t>PW</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -15321,7 +15313,7 @@
         </is>
       </c>
       <c r="B320" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
@@ -15329,19 +15321,19 @@
         </is>
       </c>
       <c r="D320" t="n">
-        <v>180</v>
+        <v>394</v>
       </c>
       <c r="E320" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F320" t="n">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="G320" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="H320" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="I320" t="n">
         <v>0.33</v>
@@ -15353,10 +15345,14 @@
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t>6I</t>
-        </is>
-      </c>
-      <c r="L320" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>8I</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -15365,34 +15361,34 @@
         </is>
       </c>
       <c r="B321" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>White</t>
         </is>
       </c>
       <c r="D321" t="n">
-        <v>411</v>
+        <v>377</v>
       </c>
       <c r="E321" t="n">
         <v>4</v>
       </c>
       <c r="F321" t="n">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="G321" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="H321" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="I321" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>Focus on Approach (Change Strategy)</t>
+          <t>No Issue</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
@@ -15402,7 +15398,7 @@
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t>7I</t>
+          <t>PW</t>
         </is>
       </c>
     </row>
@@ -15413,7 +15409,7 @@
         </is>
       </c>
       <c r="B322" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
@@ -15421,19 +15417,19 @@
         </is>
       </c>
       <c r="D322" t="n">
-        <v>344</v>
+        <v>399</v>
       </c>
       <c r="E322" t="n">
         <v>4</v>
       </c>
       <c r="F322" t="n">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="G322" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="H322" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="I322" t="n">
         <v>0.33</v>
@@ -15445,12 +15441,12 @@
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>D</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>8I</t>
         </is>
       </c>
     </row>
@@ -15461,42 +15457,46 @@
         </is>
       </c>
       <c r="B323" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>White</t>
         </is>
       </c>
       <c r="D323" t="n">
-        <v>158</v>
+        <v>381</v>
       </c>
       <c r="E323" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F323" t="n">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="G323" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
       </c>
       <c r="I323" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>Focus on Tee Shot (Change Strategy)</t>
+          <t>No Issue</t>
         </is>
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t>8I</t>
-        </is>
-      </c>
-      <c r="L323" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>PW</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -15505,7 +15505,7 @@
         </is>
       </c>
       <c r="B324" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
@@ -15513,26 +15513,26 @@
         </is>
       </c>
       <c r="D324" t="n">
-        <v>421</v>
+        <v>512</v>
       </c>
       <c r="E324" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F324" t="n">
-        <v>178</v>
+        <v>269</v>
       </c>
       <c r="G324" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="H324" t="n">
         <v>0.5</v>
       </c>
       <c r="I324" t="n">
-        <v>0.17</v>
+        <v>0.5</v>
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>Focus on Approach (Change Strategy)</t>
+          <t>No Issue</t>
         </is>
       </c>
       <c r="K324" t="inlineStr">
@@ -15542,7 +15542,7 @@
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t>6I</t>
+          <t>Layup (7I)</t>
         </is>
       </c>
     </row>
@@ -15553,30 +15553,30 @@
         </is>
       </c>
       <c r="B325" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>White</t>
         </is>
       </c>
       <c r="D325" t="n">
-        <v>549</v>
+        <v>493</v>
       </c>
       <c r="E325" t="n">
         <v>5</v>
       </c>
       <c r="F325" t="n">
-        <v>306</v>
+        <v>250</v>
       </c>
       <c r="G325" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="H325" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I325" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="J325" t="inlineStr">
         <is>
@@ -15590,45 +15590,45 @@
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t>Layup (3H)</t>
+          <t>Layup (8I)</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Swan Lake</t>
+          <t>Spring Lake Thunderbird</t>
         </is>
       </c>
       <c r="B326" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="D326" t="n">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="E326" t="n">
         <v>4</v>
       </c>
       <c r="F326" t="n">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G326" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="H326" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I326" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>Focus on Tee Shot; Approach Shot</t>
+          <t>No Issue</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
@@ -15638,18 +15638,18 @@
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>LW</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Swan Lake</t>
+          <t>Spring Lake Thunderbird</t>
         </is>
       </c>
       <c r="B327" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
@@ -15657,13 +15657,13 @@
         </is>
       </c>
       <c r="D327" t="n">
-        <v>542</v>
+        <v>315</v>
       </c>
       <c r="E327" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F327" t="n">
-        <v>299</v>
+        <v>72</v>
       </c>
       <c r="G327" t="n">
         <v>2</v>
@@ -15676,7 +15676,7 @@
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>Focus on Tee Shot; Approach Shot</t>
+          <t>No Issue</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
@@ -15686,45 +15686,45 @@
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t>Layup (3H)</t>
+          <t>LW</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Swan Lake</t>
+          <t>Spring Lake Thunderbird</t>
         </is>
       </c>
       <c r="B328" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="D328" t="n">
-        <v>419</v>
+        <v>497</v>
       </c>
       <c r="E328" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F328" t="n">
-        <v>176</v>
+        <v>254</v>
       </c>
       <c r="G328" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="H328" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I328" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>Focus on Tee Shot; Approach Shot</t>
+          <t>No Issue</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
@@ -15734,18 +15734,18 @@
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t>6I</t>
+          <t>Layup (8I)</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Swan Lake</t>
+          <t>Spring Lake Thunderbird</t>
         </is>
       </c>
       <c r="B329" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
@@ -15753,70 +15753,74 @@
         </is>
       </c>
       <c r="D329" t="n">
-        <v>181</v>
+        <v>463</v>
       </c>
       <c r="E329" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F329" t="n">
-        <v>181</v>
+        <v>220</v>
       </c>
       <c r="G329" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="H329" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I329" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>Focus on Tee Shot (Change Strategy)</t>
+          <t>No Issue</t>
         </is>
       </c>
       <c r="K329" t="inlineStr">
         <is>
-          <t>6I</t>
-        </is>
-      </c>
-      <c r="L329" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>3W</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Swan Lake</t>
+          <t>Spring Lake Thunderbird</t>
         </is>
       </c>
       <c r="B330" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="D330" t="n">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="E330" t="n">
         <v>4</v>
       </c>
       <c r="F330" t="n">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="G330" t="n">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="H330" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="I330" t="n">
         <v>0</v>
       </c>
       <c r="J330" t="inlineStr">
         <is>
-          <t>Focus on Tee Shot; Approach Shot; Putting</t>
+          <t>Focus on Approach (Change Strategy)</t>
         </is>
       </c>
       <c r="K330" t="inlineStr">
@@ -15826,18 +15830,18 @@
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>SW</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Swan Lake</t>
+          <t>Spring Lake Thunderbird</t>
         </is>
       </c>
       <c r="B331" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
@@ -15845,26 +15849,26 @@
         </is>
       </c>
       <c r="D331" t="n">
-        <v>505</v>
+        <v>318</v>
       </c>
       <c r="E331" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F331" t="n">
-        <v>262</v>
+        <v>75</v>
       </c>
       <c r="G331" t="n">
         <v>2</v>
       </c>
       <c r="H331" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I331" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>Focus on Tee Shot; Approach Shot</t>
+          <t>Focus on Approach (Change Strategy)</t>
         </is>
       </c>
       <c r="K331" t="inlineStr">
@@ -15874,50 +15878,50 @@
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t>Layup (8I)</t>
+          <t>LW</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Swan Lake</t>
+          <t>Spring Lake Thunderbird</t>
         </is>
       </c>
       <c r="B332" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="D332" t="n">
-        <v>128</v>
+        <v>180</v>
       </c>
       <c r="E332" t="n">
         <v>3</v>
       </c>
       <c r="F332" t="n">
-        <v>128</v>
+        <v>180</v>
       </c>
       <c r="G332" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
       </c>
       <c r="I332" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>Focus on Putting (Try Lag Putting)</t>
+          <t>No Issue</t>
         </is>
       </c>
       <c r="K332" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>6I</t>
         </is>
       </c>
       <c r="L332" t="inlineStr"/>
@@ -15925,11 +15929,11 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Swan Lake</t>
+          <t>Spring Lake Thunderbird</t>
         </is>
       </c>
       <c r="B333" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
@@ -15937,74 +15941,70 @@
         </is>
       </c>
       <c r="D333" t="n">
-        <v>391</v>
+        <v>154</v>
       </c>
       <c r="E333" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F333" t="n">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="G333" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="H333" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I333" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>Focus on Putting (Try Lag Putting)</t>
+          <t>No Issue</t>
         </is>
       </c>
       <c r="K333" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="L333" t="inlineStr">
-        <is>
-          <t>9I</t>
-        </is>
-      </c>
+          <t>8I</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Swan Lake</t>
+          <t>Spring Lake Thunderbird</t>
         </is>
       </c>
       <c r="B334" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="D334" t="n">
-        <v>384</v>
+        <v>411</v>
       </c>
       <c r="E334" t="n">
         <v>4</v>
       </c>
       <c r="F334" t="n">
-        <v>141</v>
+        <v>168</v>
       </c>
       <c r="G334" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="H334" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="I334" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>Approach Shot; Putting</t>
+          <t>Focus on Tee Shot; Approach Shot</t>
         </is>
       </c>
       <c r="K334" t="inlineStr">
@@ -16014,18 +16014,18 @@
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t>9I</t>
+          <t>7I</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Swan Lake</t>
+          <t>Spring Lake Thunderbird</t>
         </is>
       </c>
       <c r="B335" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C335" t="inlineStr">
         <is>
@@ -16033,16 +16033,16 @@
         </is>
       </c>
       <c r="D335" t="n">
-        <v>360</v>
+        <v>392</v>
       </c>
       <c r="E335" t="n">
         <v>4</v>
       </c>
       <c r="F335" t="n">
-        <v>117</v>
+        <v>149</v>
       </c>
       <c r="G335" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -16062,66 +16062,66 @@
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>9I</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Swan Lake</t>
+          <t>Spring Lake Thunderbird</t>
         </is>
       </c>
       <c r="B336" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="D336" t="n">
-        <v>366</v>
+        <v>344</v>
       </c>
       <c r="E336" t="n">
         <v>4</v>
       </c>
       <c r="F336" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G336" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H336" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="I336" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>Focus on Tee Shot; Approach Shot; Putting</t>
+          <t>No Issue</t>
         </is>
       </c>
       <c r="K336" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>3W</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>PW</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Swan Lake</t>
+          <t>Spring Lake Thunderbird</t>
         </is>
       </c>
       <c r="B337" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C337" t="inlineStr">
         <is>
@@ -16129,22 +16129,22 @@
         </is>
       </c>
       <c r="D337" t="n">
-        <v>475</v>
+        <v>310</v>
       </c>
       <c r="E337" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F337" t="n">
-        <v>232</v>
+        <v>67</v>
       </c>
       <c r="G337" t="n">
         <v>2</v>
       </c>
       <c r="H337" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I337" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J337" t="inlineStr">
         <is>
@@ -16158,66 +16158,62 @@
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t>Layup (5I)</t>
+          <t>LW</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Swan Lake</t>
+          <t>Spring Lake Thunderbird</t>
         </is>
       </c>
       <c r="B338" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="D338" t="n">
-        <v>305</v>
+        <v>158</v>
       </c>
       <c r="E338" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F338" t="n">
-        <v>62</v>
+        <v>158</v>
       </c>
       <c r="G338" t="n">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="H338" t="n">
         <v>0</v>
       </c>
       <c r="I338" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>Focus on Tee Shot; Approach Shot; Putting</t>
+          <t>No Issue</t>
         </is>
       </c>
       <c r="K338" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="L338" t="inlineStr">
-        <is>
-          <t>LW</t>
-        </is>
-      </c>
+          <t>8I</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Swan Lake</t>
+          <t>Spring Lake Thunderbird</t>
         </is>
       </c>
       <c r="B339" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C339" t="inlineStr">
         <is>
@@ -16225,13 +16221,13 @@
         </is>
       </c>
       <c r="D339" t="n">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="E339" t="n">
         <v>3</v>
       </c>
       <c r="F339" t="n">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="G339" t="n">
         <v>2</v>
@@ -16240,16 +16236,16 @@
         <v>0</v>
       </c>
       <c r="I339" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>Focus on Tee Shot (Change Strategy)</t>
+          <t>No Issue</t>
         </is>
       </c>
       <c r="K339" t="inlineStr">
         <is>
-          <t>3H</t>
+          <t>9I</t>
         </is>
       </c>
       <c r="L339" t="inlineStr"/>
@@ -16257,34 +16253,34 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Swan Lake</t>
+          <t>Spring Lake Thunderbird</t>
         </is>
       </c>
       <c r="B340" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="D340" t="n">
-        <v>460</v>
+        <v>421</v>
       </c>
       <c r="E340" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F340" t="n">
-        <v>217</v>
+        <v>178</v>
       </c>
       <c r="G340" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="H340" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I340" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="J340" t="inlineStr">
         <is>
@@ -16298,18 +16294,18 @@
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>6I</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Swan Lake</t>
+          <t>Spring Lake Thunderbird</t>
         </is>
       </c>
       <c r="B341" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C341" t="inlineStr">
         <is>
@@ -16317,13 +16313,13 @@
         </is>
       </c>
       <c r="D341" t="n">
-        <v>157</v>
+        <v>390</v>
       </c>
       <c r="E341" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F341" t="n">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="G341" t="n">
         <v>2</v>
@@ -16332,55 +16328,59 @@
         <v>0</v>
       </c>
       <c r="I341" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>No Issue</t>
+          <t>Focus on Approach (Change Strategy)</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t>8I</t>
-        </is>
-      </c>
-      <c r="L341" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>9I</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Swan Lake</t>
+          <t>Spring Lake Thunderbird</t>
         </is>
       </c>
       <c r="B342" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="D342" t="n">
-        <v>356</v>
+        <v>549</v>
       </c>
       <c r="E342" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F342" t="n">
-        <v>113</v>
+        <v>306</v>
       </c>
       <c r="G342" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="H342" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I342" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>Focus on Tee Shot; Approach Shot</t>
+          <t>No Issue</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
@@ -16390,14 +16390,14 @@
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>Layup (3H)</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Swan Lake</t>
+          <t>Spring Lake Thunderbird</t>
         </is>
       </c>
       <c r="B343" t="n">
@@ -16409,26 +16409,26 @@
         </is>
       </c>
       <c r="D343" t="n">
-        <v>354</v>
+        <v>519</v>
       </c>
       <c r="E343" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F343" t="n">
-        <v>111</v>
+        <v>276</v>
       </c>
       <c r="G343" t="n">
         <v>2</v>
       </c>
       <c r="H343" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I343" t="n">
         <v>0</v>
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>Focus on Tee Shot; Approach Shot</t>
+          <t>No Issue</t>
         </is>
       </c>
       <c r="K343" t="inlineStr">
@@ -16438,14 +16438,14 @@
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>Layup (6I)</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Wailea Golf Club Emerald Course</t>
+          <t>Swan Lake</t>
         </is>
       </c>
       <c r="B344" t="n">
@@ -16453,30 +16453,30 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>White</t>
         </is>
       </c>
       <c r="D344" t="n">
-        <v>354</v>
+        <v>338</v>
       </c>
       <c r="E344" t="n">
         <v>4</v>
       </c>
       <c r="F344" t="n">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="G344" t="n">
         <v>2</v>
       </c>
       <c r="H344" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I344" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J344" t="inlineStr">
         <is>
-          <t>No Issue</t>
+          <t>Focus on Tee Shot; Approach Shot</t>
         </is>
       </c>
       <c r="K344" t="inlineStr">
@@ -16486,14 +16486,14 @@
       </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>SW</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Wailea Golf Club Emerald Course</t>
+          <t>Swan Lake</t>
         </is>
       </c>
       <c r="B345" t="n">
@@ -16501,30 +16501,30 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>White</t>
         </is>
       </c>
       <c r="D345" t="n">
-        <v>484</v>
+        <v>542</v>
       </c>
       <c r="E345" t="n">
         <v>5</v>
       </c>
       <c r="F345" t="n">
-        <v>241</v>
+        <v>299</v>
       </c>
       <c r="G345" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H345" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I345" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t>Focus on Putting (Try Lag Putting)</t>
+          <t>Focus on Tee Shot; Approach Shot</t>
         </is>
       </c>
       <c r="K345" t="inlineStr">
@@ -16541,7 +16541,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Wailea Golf Club Emerald Course</t>
+          <t>Swan Lake</t>
         </is>
       </c>
       <c r="B346" t="n">
@@ -16549,20 +16549,20 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>White</t>
         </is>
       </c>
       <c r="D346" t="n">
-        <v>174</v>
+        <v>419</v>
       </c>
       <c r="E346" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F346" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G346" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="H346" t="n">
         <v>0</v>
@@ -16572,20 +16572,24 @@
       </c>
       <c r="J346" t="inlineStr">
         <is>
-          <t>Focus on Tee Shot (Change Strategy)</t>
+          <t>Focus on Tee Shot; Approach Shot</t>
         </is>
       </c>
       <c r="K346" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
           <t>6I</t>
         </is>
       </c>
-      <c r="L346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Wailea Golf Club Emerald Course</t>
+          <t>Swan Lake</t>
         </is>
       </c>
       <c r="B347" t="n">
@@ -16593,47 +16597,43 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>White</t>
         </is>
       </c>
       <c r="D347" t="n">
-        <v>344</v>
+        <v>181</v>
       </c>
       <c r="E347" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F347" t="n">
-        <v>128</v>
+        <v>181</v>
       </c>
       <c r="G347" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="H347" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I347" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t>No Issue</t>
+          <t>Focus on Tee Shot (Change Strategy)</t>
         </is>
       </c>
       <c r="K347" t="inlineStr">
         <is>
-          <t>3W</t>
-        </is>
-      </c>
-      <c r="L347" t="inlineStr">
-        <is>
-          <t>PW</t>
-        </is>
-      </c>
+          <t>6I</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Wailea Golf Club Emerald Course</t>
+          <t>Swan Lake</t>
         </is>
       </c>
       <c r="B348" t="n">
@@ -16641,30 +16641,30 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>White</t>
         </is>
       </c>
       <c r="D348" t="n">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="E348" t="n">
         <v>4</v>
       </c>
       <c r="F348" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="G348" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H348" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I348" t="n">
         <v>0</v>
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>Focus on Approach (Change Strategy)</t>
+          <t>Focus on Tee Shot; Approach Shot; Putting</t>
         </is>
       </c>
       <c r="K348" t="inlineStr">
@@ -16681,7 +16681,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Wailea Golf Club Emerald Course</t>
+          <t>Swan Lake</t>
         </is>
       </c>
       <c r="B349" t="n">
@@ -16689,30 +16689,30 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>White</t>
         </is>
       </c>
       <c r="D349" t="n">
-        <v>438</v>
+        <v>505</v>
       </c>
       <c r="E349" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F349" t="n">
-        <v>195</v>
+        <v>262</v>
       </c>
       <c r="G349" t="n">
         <v>2</v>
       </c>
       <c r="H349" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I349" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J349" t="inlineStr">
         <is>
-          <t>No Issue</t>
+          <t>Focus on Tee Shot; Approach Shot</t>
         </is>
       </c>
       <c r="K349" t="inlineStr">
@@ -16722,14 +16722,14 @@
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t>3H</t>
+          <t>Layup (7I)</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Wailea Golf Club Emerald Course</t>
+          <t>Swan Lake</t>
         </is>
       </c>
       <c r="B350" t="n">
@@ -16737,47 +16737,43 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>White</t>
         </is>
       </c>
       <c r="D350" t="n">
-        <v>378</v>
+        <v>128</v>
       </c>
       <c r="E350" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F350" t="n">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="G350" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="H350" t="n">
         <v>0</v>
       </c>
       <c r="I350" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J350" t="inlineStr">
         <is>
-          <t>Focus on Tee Shot; Approach Shot</t>
+          <t>Focus on Putting (Try Lag Putting)</t>
         </is>
       </c>
       <c r="K350" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="L350" t="inlineStr">
-        <is>
           <t>PW</t>
         </is>
       </c>
+      <c r="L350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Wailea Golf Club Emerald Course</t>
+          <t>Swan Lake</t>
         </is>
       </c>
       <c r="B351" t="n">
@@ -16785,43 +16781,47 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>White</t>
         </is>
       </c>
       <c r="D351" t="n">
-        <v>135</v>
+        <v>391</v>
       </c>
       <c r="E351" t="n">
+        <v>4</v>
+      </c>
+      <c r="F351" t="n">
+        <v>148</v>
+      </c>
+      <c r="G351" t="n">
         <v>3</v>
       </c>
-      <c r="F351" t="n">
-        <v>135</v>
-      </c>
-      <c r="G351" t="n">
-        <v>2</v>
-      </c>
       <c r="H351" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I351" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J351" t="inlineStr">
         <is>
-          <t>Focus on Tee Shot (Change Strategy)</t>
+          <t>Focus on Putting (Try Lag Putting)</t>
         </is>
       </c>
       <c r="K351" t="inlineStr">
         <is>
-          <t>PW</t>
-        </is>
-      </c>
-      <c r="L351" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>9I</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Wailea Golf Club Emerald Course</t>
+          <t>Swan Lake</t>
         </is>
       </c>
       <c r="B352" t="n">
@@ -16829,30 +16829,30 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>White</t>
         </is>
       </c>
       <c r="D352" t="n">
-        <v>496</v>
+        <v>384</v>
       </c>
       <c r="E352" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F352" t="n">
-        <v>253</v>
+        <v>141</v>
       </c>
       <c r="G352" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="H352" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I352" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J352" t="inlineStr">
         <is>
-          <t>No Issue</t>
+          <t>Approach Shot; Putting</t>
         </is>
       </c>
       <c r="K352" t="inlineStr">
@@ -16862,14 +16862,14 @@
       </c>
       <c r="L352" t="inlineStr">
         <is>
-          <t>Layup (8I)</t>
+          <t>9I</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Wailea Golf Club Emerald Course</t>
+          <t>Swan Lake</t>
         </is>
       </c>
       <c r="B353" t="n">
@@ -16877,30 +16877,30 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>White</t>
         </is>
       </c>
       <c r="D353" t="n">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="E353" t="n">
         <v>4</v>
       </c>
       <c r="F353" t="n">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="G353" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="H353" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I353" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>No Issue</t>
+          <t>Focus on Tee Shot; Approach Shot</t>
         </is>
       </c>
       <c r="K353" t="inlineStr">
@@ -16910,14 +16910,14 @@
       </c>
       <c r="L353" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Wailea Golf Club Emerald Course</t>
+          <t>Swan Lake</t>
         </is>
       </c>
       <c r="B354" t="n">
@@ -16925,30 +16925,30 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>White</t>
         </is>
       </c>
       <c r="D354" t="n">
-        <v>571</v>
+        <v>366</v>
       </c>
       <c r="E354" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F354" t="n">
-        <v>328</v>
+        <v>123</v>
       </c>
       <c r="G354" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H354" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I354" t="n">
         <v>0</v>
       </c>
       <c r="J354" t="inlineStr">
         <is>
-          <t>Focus on Approach (Change Strategy)</t>
+          <t>Focus on Tee Shot; Approach Shot; Putting</t>
         </is>
       </c>
       <c r="K354" t="inlineStr">
@@ -16958,14 +16958,14 @@
       </c>
       <c r="L354" t="inlineStr">
         <is>
-          <t>Layup (3W)</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Wailea Golf Club Emerald Course</t>
+          <t>Swan Lake</t>
         </is>
       </c>
       <c r="B355" t="n">
@@ -16973,30 +16973,30 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>White</t>
         </is>
       </c>
       <c r="D355" t="n">
-        <v>367</v>
+        <v>475</v>
       </c>
       <c r="E355" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F355" t="n">
-        <v>124</v>
+        <v>232</v>
       </c>
       <c r="G355" t="n">
         <v>2</v>
       </c>
       <c r="H355" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I355" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J355" t="inlineStr">
         <is>
-          <t>Focus on Approach (Change Strategy)</t>
+          <t>No Issue</t>
         </is>
       </c>
       <c r="K355" t="inlineStr">
@@ -17006,14 +17006,14 @@
       </c>
       <c r="L355" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>3W</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Wailea Golf Club Emerald Course</t>
+          <t>Swan Lake</t>
         </is>
       </c>
       <c r="B356" t="n">
@@ -17021,21 +17021,21 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>White</t>
         </is>
       </c>
       <c r="D356" t="n">
-        <v>139</v>
+        <v>305</v>
       </c>
       <c r="E356" t="n">
+        <v>4</v>
+      </c>
+      <c r="F356" t="n">
+        <v>62</v>
+      </c>
+      <c r="G356" t="n">
         <v>3</v>
       </c>
-      <c r="F356" t="n">
-        <v>139</v>
-      </c>
-      <c r="G356" t="n">
-        <v>2</v>
-      </c>
       <c r="H356" t="n">
         <v>0</v>
       </c>
@@ -17044,20 +17044,24 @@
       </c>
       <c r="J356" t="inlineStr">
         <is>
-          <t>Focus on Tee Shot (Change Strategy)</t>
+          <t>Focus on Tee Shot; Approach Shot; Putting</t>
         </is>
       </c>
       <c r="K356" t="inlineStr">
         <is>
-          <t>PW</t>
-        </is>
-      </c>
-      <c r="L356" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>LW</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Wailea Golf Club Emerald Course</t>
+          <t>Swan Lake</t>
         </is>
       </c>
       <c r="B357" t="n">
@@ -17065,17 +17069,17 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>White</t>
         </is>
       </c>
       <c r="D357" t="n">
-        <v>368</v>
+        <v>198</v>
       </c>
       <c r="E357" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F357" t="n">
-        <v>125</v>
+        <v>198</v>
       </c>
       <c r="G357" t="n">
         <v>2</v>
@@ -17088,24 +17092,20 @@
       </c>
       <c r="J357" t="inlineStr">
         <is>
-          <t>Focus on Tee Shot; Approach Shot</t>
+          <t>Focus on Tee Shot (Change Strategy)</t>
         </is>
       </c>
       <c r="K357" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="L357" t="inlineStr">
-        <is>
-          <t>PW</t>
-        </is>
-      </c>
+          <t>3H</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Wailea Golf Club Emerald Course</t>
+          <t>Swan Lake</t>
         </is>
       </c>
       <c r="B358" t="n">
@@ -17113,20 +17113,20 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>White</t>
         </is>
       </c>
       <c r="D358" t="n">
-        <v>395</v>
+        <v>460</v>
       </c>
       <c r="E358" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F358" t="n">
-        <v>152</v>
+        <v>217</v>
       </c>
       <c r="G358" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="H358" t="n">
         <v>1</v>
@@ -17146,14 +17146,14 @@
       </c>
       <c r="L358" t="inlineStr">
         <is>
-          <t>8I</t>
+          <t>3H</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Wailea Golf Club Emerald Course</t>
+          <t>Swan Lake</t>
         </is>
       </c>
       <c r="B359" t="n">
@@ -17161,17 +17161,17 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>White</t>
         </is>
       </c>
       <c r="D359" t="n">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="E359" t="n">
         <v>3</v>
       </c>
       <c r="F359" t="n">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="G359" t="n">
         <v>2</v>
@@ -17180,16 +17180,16 @@
         <v>0</v>
       </c>
       <c r="I359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>Focus on Tee Shot (Change Strategy)</t>
+          <t>No Issue</t>
         </is>
       </c>
       <c r="K359" t="inlineStr">
         <is>
-          <t>LAYUP (SW)</t>
+          <t>8I</t>
         </is>
       </c>
       <c r="L359" t="inlineStr"/>
@@ -17197,7 +17197,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Wailea Golf Club Emerald Course</t>
+          <t>Swan Lake</t>
         </is>
       </c>
       <c r="B360" t="n">
@@ -17205,30 +17205,30 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>White</t>
         </is>
       </c>
       <c r="D360" t="n">
-        <v>300</v>
+        <v>356</v>
       </c>
       <c r="E360" t="n">
         <v>4</v>
       </c>
       <c r="F360" t="n">
-        <v>57</v>
+        <v>113</v>
       </c>
       <c r="G360" t="n">
         <v>2</v>
       </c>
       <c r="H360" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I360" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>No Issue</t>
+          <t>Focus on Tee Shot; Approach Shot</t>
         </is>
       </c>
       <c r="K360" t="inlineStr">
@@ -17238,14 +17238,14 @@
       </c>
       <c r="L360" t="inlineStr">
         <is>
-          <t>LW</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Wailea Golf Club Emerald Course</t>
+          <t>Swan Lake</t>
         </is>
       </c>
       <c r="B361" t="n">
@@ -17253,30 +17253,30 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>White</t>
         </is>
       </c>
       <c r="D361" t="n">
-        <v>531</v>
+        <v>354</v>
       </c>
       <c r="E361" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F361" t="n">
-        <v>288</v>
+        <v>111</v>
       </c>
       <c r="G361" t="n">
         <v>2</v>
       </c>
       <c r="H361" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I361" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>No Issue</t>
+          <t>Focus on Tee Shot; Approach Shot</t>
         </is>
       </c>
       <c r="K361" t="inlineStr">
@@ -17286,14 +17286,14 @@
       </c>
       <c r="L361" t="inlineStr">
         <is>
-          <t>Layup (3H)</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Wailea Golf Club Gold Course</t>
+          <t>Wailea Golf Club Emerald Course</t>
         </is>
       </c>
       <c r="B362" t="n">
@@ -17305,13 +17305,13 @@
         </is>
       </c>
       <c r="D362" t="n">
-        <v>400</v>
+        <v>354</v>
       </c>
       <c r="E362" t="n">
         <v>4</v>
       </c>
       <c r="F362" t="n">
-        <v>157</v>
+        <v>111</v>
       </c>
       <c r="G362" t="n">
         <v>2</v>
@@ -17320,11 +17320,11 @@
         <v>0.5</v>
       </c>
       <c r="I362" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>Focus on Approach (Change Strategy)</t>
+          <t>No Issue</t>
         </is>
       </c>
       <c r="K362" t="inlineStr">
@@ -17334,14 +17334,14 @@
       </c>
       <c r="L362" t="inlineStr">
         <is>
-          <t>8I</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Wailea Golf Club Gold Course</t>
+          <t>Wailea Golf Club Emerald Course</t>
         </is>
       </c>
       <c r="B363" t="n">
@@ -17353,16 +17353,16 @@
         </is>
       </c>
       <c r="D363" t="n">
-        <v>500</v>
+        <v>484</v>
       </c>
       <c r="E363" t="n">
         <v>5</v>
       </c>
       <c r="F363" t="n">
-        <v>257</v>
+        <v>241</v>
       </c>
       <c r="G363" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="H363" t="n">
         <v>0.5</v>
@@ -17372,7 +17372,7 @@
       </c>
       <c r="J363" t="inlineStr">
         <is>
-          <t>No Issue</t>
+          <t>Focus on Putting (Try Lag Putting)</t>
         </is>
       </c>
       <c r="K363" t="inlineStr">
@@ -17382,14 +17382,14 @@
       </c>
       <c r="L363" t="inlineStr">
         <is>
-          <t>Layup (8I)</t>
+          <t>Layup (3H)</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Wailea Golf Club Gold Course</t>
+          <t>Wailea Golf Club Emerald Course</t>
         </is>
       </c>
       <c r="B364" t="n">
@@ -17401,16 +17401,16 @@
         </is>
       </c>
       <c r="D364" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E364" t="n">
         <v>3</v>
       </c>
       <c r="F364" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G364" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="H364" t="n">
         <v>0</v>
@@ -17433,7 +17433,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Wailea Golf Club Gold Course</t>
+          <t>Wailea Golf Club Emerald Course</t>
         </is>
       </c>
       <c r="B365" t="n">
@@ -17445,23 +17445,23 @@
         </is>
       </c>
       <c r="D365" t="n">
-        <v>393</v>
+        <v>344</v>
       </c>
       <c r="E365" t="n">
         <v>4</v>
       </c>
       <c r="F365" t="n">
-        <v>177</v>
+        <v>125</v>
       </c>
       <c r="G365" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="H365" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I365" t="n">
         <v>1</v>
       </c>
-      <c r="I365" t="n">
-        <v>0.5</v>
-      </c>
       <c r="J365" t="inlineStr">
         <is>
           <t>No Issue</t>
@@ -17474,14 +17474,14 @@
       </c>
       <c r="L365" t="inlineStr">
         <is>
-          <t>6I</t>
+          <t>PW</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Wailea Golf Club Gold Course</t>
+          <t>Wailea Golf Club Emerald Course</t>
         </is>
       </c>
       <c r="B366" t="n">
@@ -17493,26 +17493,26 @@
         </is>
       </c>
       <c r="D366" t="n">
-        <v>428</v>
+        <v>352</v>
       </c>
       <c r="E366" t="n">
         <v>4</v>
       </c>
       <c r="F366" t="n">
-        <v>185</v>
+        <v>109</v>
       </c>
       <c r="G366" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="H366" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I366" t="n">
         <v>0</v>
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>Focus on Tee Shot; Approach Shot</t>
+          <t>Focus on Approach (Change Strategy)</t>
         </is>
       </c>
       <c r="K366" t="inlineStr">
@@ -17522,14 +17522,14 @@
       </c>
       <c r="L366" t="inlineStr">
         <is>
-          <t>5I</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Wailea Golf Club Gold Course</t>
+          <t>Wailea Golf Club Emerald Course</t>
         </is>
       </c>
       <c r="B367" t="n">
@@ -17541,43 +17541,43 @@
         </is>
       </c>
       <c r="D367" t="n">
-        <v>264</v>
+        <v>438</v>
       </c>
       <c r="E367" t="n">
         <v>4</v>
       </c>
       <c r="F367" t="n">
-        <v>48</v>
+        <v>195</v>
       </c>
       <c r="G367" t="n">
         <v>2</v>
       </c>
       <c r="H367" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I367" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>Work on Tee Shot (Change Strategy)</t>
+          <t>No Issue</t>
         </is>
       </c>
       <c r="K367" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>D</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
         <is>
-          <t>LW</t>
+          <t>3H</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Wailea Golf Club Gold Course</t>
+          <t>Wailea Golf Club Emerald Course</t>
         </is>
       </c>
       <c r="B368" t="n">
@@ -17589,26 +17589,26 @@
         </is>
       </c>
       <c r="D368" t="n">
-        <v>567</v>
+        <v>378</v>
       </c>
       <c r="E368" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F368" t="n">
-        <v>324</v>
+        <v>135</v>
       </c>
       <c r="G368" t="n">
         <v>1.5</v>
       </c>
       <c r="H368" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I368" t="n">
         <v>0</v>
       </c>
       <c r="J368" t="inlineStr">
         <is>
-          <t>Focus on Approach (Change Strategy)</t>
+          <t>Focus on Tee Shot; Approach Shot</t>
         </is>
       </c>
       <c r="K368" t="inlineStr">
@@ -17618,14 +17618,14 @@
       </c>
       <c r="L368" t="inlineStr">
         <is>
-          <t>Layup (3W)</t>
+          <t>PW</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Wailea Golf Club Gold Course</t>
+          <t>Wailea Golf Club Emerald Course</t>
         </is>
       </c>
       <c r="B369" t="n">
@@ -17637,13 +17637,13 @@
         </is>
       </c>
       <c r="D369" t="n">
-        <v>188</v>
+        <v>135</v>
       </c>
       <c r="E369" t="n">
         <v>3</v>
       </c>
       <c r="F369" t="n">
-        <v>188</v>
+        <v>135</v>
       </c>
       <c r="G369" t="n">
         <v>2</v>
@@ -17652,16 +17652,16 @@
         <v>0</v>
       </c>
       <c r="I369" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>No Issue</t>
+          <t>Focus on Tee Shot (Change Strategy)</t>
         </is>
       </c>
       <c r="K369" t="inlineStr">
         <is>
-          <t>5I</t>
+          <t>PW</t>
         </is>
       </c>
       <c r="L369" t="inlineStr"/>
@@ -17669,7 +17669,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Wailea Golf Club Gold Course</t>
+          <t>Wailea Golf Club Emerald Course</t>
         </is>
       </c>
       <c r="B370" t="n">
@@ -17681,26 +17681,26 @@
         </is>
       </c>
       <c r="D370" t="n">
-        <v>333</v>
+        <v>496</v>
       </c>
       <c r="E370" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F370" t="n">
-        <v>90</v>
+        <v>253</v>
       </c>
       <c r="G370" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="H370" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I370" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>Focus on Approach (Change Strategy)</t>
+          <t>No Issue</t>
         </is>
       </c>
       <c r="K370" t="inlineStr">
@@ -17710,14 +17710,14 @@
       </c>
       <c r="L370" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>Layup (8I)</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Wailea Golf Club Gold Course</t>
+          <t>Wailea Golf Club Emerald Course</t>
         </is>
       </c>
       <c r="B371" t="n">
@@ -17729,26 +17729,26 @@
         </is>
       </c>
       <c r="D371" t="n">
-        <v>397</v>
+        <v>369</v>
       </c>
       <c r="E371" t="n">
         <v>4</v>
       </c>
       <c r="F371" t="n">
-        <v>154</v>
+        <v>126</v>
       </c>
       <c r="G371" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="H371" t="n">
         <v>1</v>
       </c>
       <c r="I371" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>Focus on Approach (Change Strategy)</t>
+          <t>No Issue</t>
         </is>
       </c>
       <c r="K371" t="inlineStr">
@@ -17758,14 +17758,14 @@
       </c>
       <c r="L371" t="inlineStr">
         <is>
-          <t>8I</t>
+          <t>PW</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Wailea Golf Club Gold Course</t>
+          <t>Wailea Golf Club Emerald Course</t>
         </is>
       </c>
       <c r="B372" t="n">
@@ -17777,39 +17777,43 @@
         </is>
       </c>
       <c r="D372" t="n">
-        <v>159</v>
+        <v>571</v>
       </c>
       <c r="E372" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F372" t="n">
-        <v>159</v>
+        <v>328</v>
       </c>
       <c r="G372" t="n">
         <v>2</v>
       </c>
       <c r="H372" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I372" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J372" t="inlineStr">
         <is>
-          <t>No Issue</t>
+          <t>Focus on Approach (Change Strategy)</t>
         </is>
       </c>
       <c r="K372" t="inlineStr">
         <is>
-          <t>8I</t>
-        </is>
-      </c>
-      <c r="L372" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>Layup (3W)</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Wailea Golf Club Gold Course</t>
+          <t>Wailea Golf Club Emerald Course</t>
         </is>
       </c>
       <c r="B373" t="n">
@@ -17821,26 +17825,26 @@
         </is>
       </c>
       <c r="D373" t="n">
-        <v>470</v>
+        <v>367</v>
       </c>
       <c r="E373" t="n">
         <v>4</v>
       </c>
       <c r="F373" t="n">
-        <v>227</v>
+        <v>124</v>
       </c>
       <c r="G373" t="n">
         <v>2</v>
       </c>
       <c r="H373" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I373" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>Work on Tee Shot (Change Strategy)</t>
+          <t>Focus on Approach (Change Strategy)</t>
         </is>
       </c>
       <c r="K373" t="inlineStr">
@@ -17850,14 +17854,14 @@
       </c>
       <c r="L373" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>PW</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Wailea Golf Club Gold Course</t>
+          <t>Wailea Golf Club Emerald Course</t>
         </is>
       </c>
       <c r="B374" t="n">
@@ -17869,16 +17873,16 @@
         </is>
       </c>
       <c r="D374" t="n">
-        <v>514</v>
+        <v>139</v>
       </c>
       <c r="E374" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F374" t="n">
-        <v>271</v>
+        <v>139</v>
       </c>
       <c r="G374" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -17888,24 +17892,20 @@
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>Focus on Tee Shot; Approach Shot</t>
+          <t>Focus on Tee Shot (Change Strategy)</t>
         </is>
       </c>
       <c r="K374" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="L374" t="inlineStr">
-        <is>
-          <t>Layup (7I)</t>
-        </is>
-      </c>
+          <t>PW</t>
+        </is>
+      </c>
+      <c r="L374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Wailea Golf Club Gold Course</t>
+          <t>Wailea Golf Club Emerald Course</t>
         </is>
       </c>
       <c r="B375" t="n">
@@ -17917,16 +17917,16 @@
         </is>
       </c>
       <c r="D375" t="n">
-        <v>420</v>
+        <v>368</v>
       </c>
       <c r="E375" t="n">
         <v>4</v>
       </c>
       <c r="F375" t="n">
-        <v>177</v>
+        <v>125</v>
       </c>
       <c r="G375" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="H375" t="n">
         <v>0</v>
@@ -17946,14 +17946,14 @@
       </c>
       <c r="L375" t="inlineStr">
         <is>
-          <t>6I</t>
+          <t>PW</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Wailea Golf Club Gold Course</t>
+          <t>Wailea Golf Club Emerald Course</t>
         </is>
       </c>
       <c r="B376" t="n">
@@ -17965,26 +17965,26 @@
         </is>
       </c>
       <c r="D376" t="n">
-        <v>507</v>
+        <v>395</v>
       </c>
       <c r="E376" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F376" t="n">
-        <v>264</v>
+        <v>152</v>
       </c>
       <c r="G376" t="n">
         <v>1.5</v>
       </c>
       <c r="H376" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I376" t="n">
         <v>0</v>
       </c>
       <c r="J376" t="inlineStr">
         <is>
-          <t>Focus on Tee Shot; Approach Shot</t>
+          <t>Focus on Approach (Change Strategy)</t>
         </is>
       </c>
       <c r="K376" t="inlineStr">
@@ -17994,14 +17994,14 @@
       </c>
       <c r="L376" t="inlineStr">
         <is>
-          <t>Layup (7I)</t>
+          <t>8I</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Wailea Golf Club Gold Course</t>
+          <t>Wailea Golf Club Emerald Course</t>
         </is>
       </c>
       <c r="B377" t="n">
@@ -18013,13 +18013,13 @@
         </is>
       </c>
       <c r="D377" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="E377" t="n">
         <v>3</v>
       </c>
       <c r="F377" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="G377" t="n">
         <v>2</v>
@@ -18037,7 +18037,7 @@
       </c>
       <c r="K377" t="inlineStr">
         <is>
-          <t>6I</t>
+          <t>8I</t>
         </is>
       </c>
       <c r="L377" t="inlineStr"/>
@@ -18045,7 +18045,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Wailea Golf Club Gold Course</t>
+          <t>Wailea Golf Club Emerald Course</t>
         </is>
       </c>
       <c r="B378" t="n">
@@ -18057,13 +18057,13 @@
         </is>
       </c>
       <c r="D378" t="n">
-        <v>348</v>
+        <v>300</v>
       </c>
       <c r="E378" t="n">
         <v>4</v>
       </c>
       <c r="F378" t="n">
-        <v>105</v>
+        <v>57</v>
       </c>
       <c r="G378" t="n">
         <v>2</v>
@@ -18072,11 +18072,11 @@
         <v>0.5</v>
       </c>
       <c r="I378" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J378" t="inlineStr">
         <is>
-          <t>Focus on Approach (Change Strategy)</t>
+          <t>No Issue</t>
         </is>
       </c>
       <c r="K378" t="inlineStr">
@@ -18086,14 +18086,14 @@
       </c>
       <c r="L378" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>LW</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Wailea Golf Club Gold Course</t>
+          <t>Wailea Golf Club Emerald Course</t>
         </is>
       </c>
       <c r="B379" t="n">
@@ -18105,26 +18105,26 @@
         </is>
       </c>
       <c r="D379" t="n">
-        <v>409</v>
+        <v>531</v>
       </c>
       <c r="E379" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F379" t="n">
-        <v>166</v>
+        <v>288</v>
       </c>
       <c r="G379" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="H379" t="n">
         <v>0.5</v>
       </c>
       <c r="I379" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J379" t="inlineStr">
         <is>
-          <t>Focus on Approach (Change Strategy)</t>
+          <t>No Issue</t>
         </is>
       </c>
       <c r="K379" t="inlineStr">
@@ -18134,14 +18134,14 @@
       </c>
       <c r="L379" t="inlineStr">
         <is>
-          <t>7I</t>
+          <t>Layup (5I)</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Willow Creek Hamlet Course</t>
+          <t>Wailea Golf Club Gold Course</t>
         </is>
       </c>
       <c r="B380" t="n">
@@ -18153,16 +18153,16 @@
         </is>
       </c>
       <c r="D380" t="n">
-        <v>298</v>
+        <v>400</v>
       </c>
       <c r="E380" t="n">
         <v>4</v>
       </c>
       <c r="F380" t="n">
-        <v>55</v>
+        <v>157</v>
       </c>
       <c r="G380" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="H380" t="n">
         <v>0.5</v>
@@ -18182,14 +18182,14 @@
       </c>
       <c r="L380" t="inlineStr">
         <is>
-          <t>LW</t>
+          <t>8I</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Willow Creek Hamlet Course</t>
+          <t>Wailea Golf Club Gold Course</t>
         </is>
       </c>
       <c r="B381" t="n">
@@ -18201,22 +18201,22 @@
         </is>
       </c>
       <c r="D381" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="E381" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F381" t="n">
-        <v>130</v>
+        <v>257</v>
       </c>
       <c r="G381" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="H381" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I381" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="J381" t="inlineStr">
         <is>
@@ -18225,15 +18225,19 @@
       </c>
       <c r="K381" t="inlineStr">
         <is>
-          <t>PW</t>
-        </is>
-      </c>
-      <c r="L381" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>Layup (8I)</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Willow Creek Hamlet Course</t>
+          <t>Wailea Golf Club Gold Course</t>
         </is>
       </c>
       <c r="B382" t="n">
@@ -18245,43 +18249,39 @@
         </is>
       </c>
       <c r="D382" t="n">
-        <v>327</v>
+        <v>176</v>
       </c>
       <c r="E382" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F382" t="n">
-        <v>84</v>
+        <v>176</v>
       </c>
       <c r="G382" t="n">
         <v>2</v>
       </c>
       <c r="H382" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="I382" t="n">
         <v>0</v>
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>Focus on Tee Shot; Approach Shot</t>
+          <t>Focus on Tee Shot (Change Strategy)</t>
         </is>
       </c>
       <c r="K382" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="L382" t="inlineStr">
-        <is>
-          <t>SW</t>
-        </is>
-      </c>
+          <t>6I</t>
+        </is>
+      </c>
+      <c r="L382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Willow Creek Hamlet Course</t>
+          <t>Wailea Golf Club Gold Course</t>
         </is>
       </c>
       <c r="B383" t="n">
@@ -18293,39 +18293,43 @@
         </is>
       </c>
       <c r="D383" t="n">
-        <v>176</v>
+        <v>393</v>
       </c>
       <c r="E383" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F383" t="n">
-        <v>176</v>
+        <v>150</v>
       </c>
       <c r="G383" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="H383" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I383" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>Focus on Tee Shot (Change Strategy)</t>
+          <t>No Issue</t>
         </is>
       </c>
       <c r="K383" t="inlineStr">
         <is>
-          <t>6I</t>
-        </is>
-      </c>
-      <c r="L383" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>8I</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Willow Creek Hamlet Course</t>
+          <t>Wailea Golf Club Gold Course</t>
         </is>
       </c>
       <c r="B384" t="n">
@@ -18337,26 +18341,26 @@
         </is>
       </c>
       <c r="D384" t="n">
-        <v>457</v>
+        <v>428</v>
       </c>
       <c r="E384" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F384" t="n">
-        <v>214</v>
+        <v>185</v>
       </c>
       <c r="G384" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="H384" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="I384" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>Work on Tee Shot (Change Strategy)</t>
+          <t>Focus on Tee Shot; Approach Shot</t>
         </is>
       </c>
       <c r="K384" t="inlineStr">
@@ -18366,14 +18370,14 @@
       </c>
       <c r="L384" t="inlineStr">
         <is>
-          <t>3H</t>
+          <t>5I</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Willow Creek Hamlet Course</t>
+          <t>Wailea Golf Club Gold Course</t>
         </is>
       </c>
       <c r="B385" t="n">
@@ -18385,43 +18389,43 @@
         </is>
       </c>
       <c r="D385" t="n">
-        <v>389</v>
+        <v>264</v>
       </c>
       <c r="E385" t="n">
         <v>4</v>
       </c>
       <c r="F385" t="n">
-        <v>146</v>
+        <v>45</v>
       </c>
       <c r="G385" t="n">
         <v>2</v>
       </c>
       <c r="H385" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="I385" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>Focus on Tee Shot; Approach Shot</t>
+          <t>Work on Tee Shot (Change Strategy)</t>
         </is>
       </c>
       <c r="K385" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>3W</t>
         </is>
       </c>
       <c r="L385" t="inlineStr">
         <is>
-          <t>9I</t>
+          <t>LW</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Willow Creek Hamlet Course</t>
+          <t>Wailea Golf Club Gold Course</t>
         </is>
       </c>
       <c r="B386" t="n">
@@ -18433,26 +18437,26 @@
         </is>
       </c>
       <c r="D386" t="n">
-        <v>301</v>
+        <v>567</v>
       </c>
       <c r="E386" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F386" t="n">
-        <v>58</v>
+        <v>324</v>
       </c>
       <c r="G386" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="H386" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="I386" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>No Issue</t>
+          <t>Focus on Approach (Change Strategy)</t>
         </is>
       </c>
       <c r="K386" t="inlineStr">
@@ -18462,14 +18466,14 @@
       </c>
       <c r="L386" t="inlineStr">
         <is>
-          <t>LW</t>
+          <t>Layup (3W)</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Willow Creek Hamlet Course</t>
+          <t>Wailea Golf Club Gold Course</t>
         </is>
       </c>
       <c r="B387" t="n">
@@ -18481,43 +18485,39 @@
         </is>
       </c>
       <c r="D387" t="n">
-        <v>356</v>
+        <v>188</v>
       </c>
       <c r="E387" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F387" t="n">
-        <v>113</v>
+        <v>188</v>
       </c>
       <c r="G387" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="H387" t="n">
         <v>0</v>
       </c>
       <c r="I387" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>Focus on Tee Shot; Approach Shot</t>
+          <t>No Issue</t>
         </is>
       </c>
       <c r="K387" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="L387" t="inlineStr">
-        <is>
-          <t>GW</t>
-        </is>
-      </c>
+          <t>5I</t>
+        </is>
+      </c>
+      <c r="L387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Willow Creek Hamlet Course</t>
+          <t>Wailea Golf Club Gold Course</t>
         </is>
       </c>
       <c r="B388" t="n">
@@ -18529,26 +18529,26 @@
         </is>
       </c>
       <c r="D388" t="n">
-        <v>534</v>
+        <v>333</v>
       </c>
       <c r="E388" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F388" t="n">
-        <v>291</v>
+        <v>90</v>
       </c>
       <c r="G388" t="n">
         <v>2</v>
       </c>
       <c r="H388" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="I388" t="n">
         <v>0</v>
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>Focus on Tee Shot; Approach Shot</t>
+          <t>Focus on Approach (Change Strategy)</t>
         </is>
       </c>
       <c r="K388" t="inlineStr">
@@ -18558,14 +18558,14 @@
       </c>
       <c r="L388" t="inlineStr">
         <is>
-          <t>Layup (3H)</t>
+          <t>SW</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Willow Creek Hamlet Course</t>
+          <t>Wailea Golf Club Gold Course</t>
         </is>
       </c>
       <c r="B389" t="n">
@@ -18577,26 +18577,26 @@
         </is>
       </c>
       <c r="D389" t="n">
-        <v>339</v>
+        <v>397</v>
       </c>
       <c r="E389" t="n">
         <v>4</v>
       </c>
       <c r="F389" t="n">
-        <v>96</v>
+        <v>154</v>
       </c>
       <c r="G389" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="H389" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="I389" t="n">
         <v>0</v>
       </c>
       <c r="J389" t="inlineStr">
         <is>
-          <t>Focus on Tee Shot; Approach Shot</t>
+          <t>Focus on Approach (Change Strategy)</t>
         </is>
       </c>
       <c r="K389" t="inlineStr">
@@ -18606,14 +18606,14 @@
       </c>
       <c r="L389" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>8I</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Willow Creek Hamlet Course</t>
+          <t>Wailea Golf Club Gold Course</t>
         </is>
       </c>
       <c r="B390" t="n">
@@ -18625,13 +18625,13 @@
         </is>
       </c>
       <c r="D390" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E390" t="n">
         <v>3</v>
       </c>
       <c r="F390" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G390" t="n">
         <v>2</v>
@@ -18640,11 +18640,11 @@
         <v>0</v>
       </c>
       <c r="I390" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>Focus on Tee Shot (Change Strategy)</t>
+          <t>No Issue</t>
         </is>
       </c>
       <c r="K390" t="inlineStr">
@@ -18657,7 +18657,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Willow Creek Hamlet Course</t>
+          <t>Wailea Golf Club Gold Course</t>
         </is>
       </c>
       <c r="B391" t="n">
@@ -18669,22 +18669,22 @@
         </is>
       </c>
       <c r="D391" t="n">
-        <v>363</v>
+        <v>470</v>
       </c>
       <c r="E391" t="n">
         <v>4</v>
       </c>
       <c r="F391" t="n">
-        <v>120</v>
+        <v>227</v>
       </c>
       <c r="G391" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="H391" t="n">
         <v>0</v>
       </c>
       <c r="I391" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="J391" t="inlineStr">
         <is>
@@ -18698,14 +18698,14 @@
       </c>
       <c r="L391" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>3W</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Willow Creek Hamlet Course</t>
+          <t>Wailea Golf Club Gold Course</t>
         </is>
       </c>
       <c r="B392" t="n">
@@ -18717,26 +18717,26 @@
         </is>
       </c>
       <c r="D392" t="n">
-        <v>555</v>
+        <v>514</v>
       </c>
       <c r="E392" t="n">
         <v>5</v>
       </c>
       <c r="F392" t="n">
-        <v>312</v>
+        <v>271</v>
       </c>
       <c r="G392" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="H392" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="I392" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J392" t="inlineStr">
         <is>
-          <t>Work on Tee Shot (Change Strategy)</t>
+          <t>Focus on Tee Shot; Approach Shot</t>
         </is>
       </c>
       <c r="K392" t="inlineStr">
@@ -18746,14 +18746,14 @@
       </c>
       <c r="L392" t="inlineStr">
         <is>
-          <t>Layup (3H)</t>
+          <t>Layup (7I)</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Willow Creek Hamlet Course</t>
+          <t>Wailea Golf Club Gold Course</t>
         </is>
       </c>
       <c r="B393" t="n">
@@ -18765,39 +18765,43 @@
         </is>
       </c>
       <c r="D393" t="n">
-        <v>172</v>
+        <v>420</v>
       </c>
       <c r="E393" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F393" t="n">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="G393" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="H393" t="n">
         <v>0</v>
       </c>
       <c r="I393" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>No Issue</t>
+          <t>Focus on Tee Shot; Approach Shot</t>
         </is>
       </c>
       <c r="K393" t="inlineStr">
         <is>
-          <t>7I</t>
-        </is>
-      </c>
-      <c r="L393" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>6I</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Willow Creek Hamlet Course</t>
+          <t>Wailea Golf Club Gold Course</t>
         </is>
       </c>
       <c r="B394" t="n">
@@ -18809,16 +18813,16 @@
         </is>
       </c>
       <c r="D394" t="n">
-        <v>527</v>
+        <v>507</v>
       </c>
       <c r="E394" t="n">
         <v>5</v>
       </c>
       <c r="F394" t="n">
-        <v>284</v>
+        <v>264</v>
       </c>
       <c r="G394" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="H394" t="n">
         <v>0</v>
@@ -18838,14 +18842,14 @@
       </c>
       <c r="L394" t="inlineStr">
         <is>
-          <t>Layup (5I)</t>
+          <t>Layup (7I)</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Willow Creek Hamlet Course</t>
+          <t>Wailea Golf Club Gold Course</t>
         </is>
       </c>
       <c r="B395" t="n">
@@ -18857,16 +18861,16 @@
         </is>
       </c>
       <c r="D395" t="n">
-        <v>137</v>
+        <v>180</v>
       </c>
       <c r="E395" t="n">
         <v>3</v>
       </c>
       <c r="F395" t="n">
-        <v>137</v>
+        <v>180</v>
       </c>
       <c r="G395" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="H395" t="n">
         <v>0</v>
@@ -18881,7 +18885,7 @@
       </c>
       <c r="K395" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>6I</t>
         </is>
       </c>
       <c r="L395" t="inlineStr"/>
@@ -18889,7 +18893,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Willow Creek Hamlet Course</t>
+          <t>Wailea Golf Club Gold Course</t>
         </is>
       </c>
       <c r="B396" t="n">
@@ -18901,26 +18905,26 @@
         </is>
       </c>
       <c r="D396" t="n">
-        <v>394</v>
+        <v>348</v>
       </c>
       <c r="E396" t="n">
         <v>4</v>
       </c>
       <c r="F396" t="n">
-        <v>151</v>
+        <v>105</v>
       </c>
       <c r="G396" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="H396" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="I396" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>No Issue</t>
+          <t>Focus on Approach (Change Strategy)</t>
         </is>
       </c>
       <c r="K396" t="inlineStr">
@@ -18930,14 +18934,14 @@
       </c>
       <c r="L396" t="inlineStr">
         <is>
-          <t>8I</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Willow Creek Hamlet Course</t>
+          <t>Wailea Golf Club Gold Course</t>
         </is>
       </c>
       <c r="B397" t="n">
@@ -18949,26 +18953,26 @@
         </is>
       </c>
       <c r="D397" t="n">
-        <v>385</v>
+        <v>409</v>
       </c>
       <c r="E397" t="n">
         <v>4</v>
       </c>
       <c r="F397" t="n">
-        <v>142</v>
+        <v>166</v>
       </c>
       <c r="G397" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="H397" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I397" t="n">
         <v>0</v>
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>Focus on Tee Shot; Approach Shot</t>
+          <t>Focus on Approach (Change Strategy)</t>
         </is>
       </c>
       <c r="K397" t="inlineStr">
@@ -18978,14 +18982,14 @@
       </c>
       <c r="L397" t="inlineStr">
         <is>
-          <t>9I</t>
+          <t>7I</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Wind Watch Hamlet Course</t>
+          <t>Willow Creek Hamlet Course</t>
         </is>
       </c>
       <c r="B398" t="n">
@@ -18997,26 +19001,26 @@
         </is>
       </c>
       <c r="D398" t="n">
-        <v>360</v>
+        <v>298</v>
       </c>
       <c r="E398" t="n">
         <v>4</v>
       </c>
       <c r="F398" t="n">
-        <v>117</v>
+        <v>55</v>
       </c>
       <c r="G398" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="H398" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="I398" t="n">
         <v>0</v>
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>Focus on Tee Shot; Approach Shot</t>
+          <t>Focus on Approach (Change Strategy)</t>
         </is>
       </c>
       <c r="K398" t="inlineStr">
@@ -19026,66 +19030,62 @@
       </c>
       <c r="L398" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>LW</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Wind Watch Hamlet Course</t>
+          <t>Willow Creek Hamlet Course</t>
         </is>
       </c>
       <c r="B399" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="D399" t="n">
-        <v>359</v>
+        <v>130</v>
       </c>
       <c r="E399" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F399" t="n">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="G399" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="H399" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I399" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>Focus on Tee Shot; Approach Shot</t>
+          <t>No Issue</t>
         </is>
       </c>
       <c r="K399" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="L399" t="inlineStr">
-        <is>
-          <t>GW</t>
-        </is>
-      </c>
+          <t>PW</t>
+        </is>
+      </c>
+      <c r="L399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Wind Watch Hamlet Course</t>
+          <t>Willow Creek Hamlet Course</t>
         </is>
       </c>
       <c r="B400" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C400" t="inlineStr">
         <is>
@@ -19093,26 +19093,26 @@
         </is>
       </c>
       <c r="D400" t="n">
-        <v>480</v>
+        <v>327</v>
       </c>
       <c r="E400" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F400" t="n">
-        <v>237</v>
+        <v>84</v>
       </c>
       <c r="G400" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="H400" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I400" t="n">
         <v>0</v>
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>Focus on Approach (Change Strategy)</t>
+          <t>Focus on Tee Shot; Approach Shot</t>
         </is>
       </c>
       <c r="K400" t="inlineStr">
@@ -19122,66 +19122,62 @@
       </c>
       <c r="L400" t="inlineStr">
         <is>
-          <t>Layup (5I)</t>
+          <t>LW</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Wind Watch Hamlet Course</t>
+          <t>Willow Creek Hamlet Course</t>
         </is>
       </c>
       <c r="B401" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="D401" t="n">
-        <v>440</v>
+        <v>176</v>
       </c>
       <c r="E401" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F401" t="n">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="G401" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="H401" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I401" t="n">
         <v>0</v>
       </c>
       <c r="J401" t="inlineStr">
         <is>
-          <t>Focus on Approach (Change Strategy)</t>
+          <t>Focus on Tee Shot (Change Strategy)</t>
         </is>
       </c>
       <c r="K401" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="L401" t="inlineStr">
-        <is>
-          <t>3H</t>
-        </is>
-      </c>
+          <t>6I</t>
+        </is>
+      </c>
+      <c r="L401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Wind Watch Hamlet Course</t>
+          <t>Willow Creek Hamlet Course</t>
         </is>
       </c>
       <c r="B402" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C402" t="inlineStr">
         <is>
@@ -19189,26 +19185,26 @@
         </is>
       </c>
       <c r="D402" t="n">
-        <v>315</v>
+        <v>457</v>
       </c>
       <c r="E402" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F402" t="n">
-        <v>72</v>
+        <v>214</v>
       </c>
       <c r="G402" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="H402" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I402" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="J402" t="inlineStr">
         <is>
-          <t>Focus on Tee Shot; Approach Shot</t>
+          <t>Work on Tee Shot (Change Strategy)</t>
         </is>
       </c>
       <c r="K402" t="inlineStr">
@@ -19218,38 +19214,38 @@
       </c>
       <c r="L402" t="inlineStr">
         <is>
-          <t>LW</t>
+          <t>3H</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Wind Watch Hamlet Course</t>
+          <t>Willow Creek Hamlet Course</t>
         </is>
       </c>
       <c r="B403" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="D403" t="n">
-        <v>325</v>
+        <v>389</v>
       </c>
       <c r="E403" t="n">
         <v>4</v>
       </c>
       <c r="F403" t="n">
-        <v>82</v>
+        <v>146</v>
       </c>
       <c r="G403" t="n">
         <v>2</v>
       </c>
       <c r="H403" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="I403" t="n">
         <v>0</v>
@@ -19266,18 +19262,18 @@
       </c>
       <c r="L403" t="inlineStr">
         <is>
-          <t>LW</t>
+          <t>9I</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Wind Watch Hamlet Course</t>
+          <t>Willow Creek Hamlet Course</t>
         </is>
       </c>
       <c r="B404" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C404" t="inlineStr">
         <is>
@@ -19285,26 +19281,26 @@
         </is>
       </c>
       <c r="D404" t="n">
-        <v>375</v>
+        <v>301</v>
       </c>
       <c r="E404" t="n">
         <v>4</v>
       </c>
       <c r="F404" t="n">
-        <v>132</v>
+        <v>58</v>
       </c>
       <c r="G404" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="H404" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="I404" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J404" t="inlineStr">
         <is>
-          <t>Focus on Tee Shot; Approach Shot</t>
+          <t>No Issue</t>
         </is>
       </c>
       <c r="K404" t="inlineStr">
@@ -19314,38 +19310,38 @@
       </c>
       <c r="L404" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>LW</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Wind Watch Hamlet Course</t>
+          <t>Willow Creek Hamlet Course</t>
         </is>
       </c>
       <c r="B405" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="D405" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="E405" t="n">
         <v>4</v>
       </c>
       <c r="F405" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G405" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="H405" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I405" t="n">
         <v>0</v>
@@ -19369,11 +19365,11 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Wind Watch Hamlet Course</t>
+          <t>Willow Creek Hamlet Course</t>
         </is>
       </c>
       <c r="B406" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C406" t="inlineStr">
         <is>
@@ -19381,26 +19377,26 @@
         </is>
       </c>
       <c r="D406" t="n">
-        <v>478</v>
+        <v>534</v>
       </c>
       <c r="E406" t="n">
         <v>5</v>
       </c>
       <c r="F406" t="n">
-        <v>235</v>
+        <v>291</v>
       </c>
       <c r="G406" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="H406" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="I406" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J406" t="inlineStr">
         <is>
-          <t>No Issue</t>
+          <t>Focus on Tee Shot; Approach Shot</t>
         </is>
       </c>
       <c r="K406" t="inlineStr">
@@ -19410,45 +19406,45 @@
       </c>
       <c r="L406" t="inlineStr">
         <is>
-          <t>Layup (5I)</t>
+          <t>Layup (3H)</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Wind Watch Hamlet Course</t>
+          <t>Willow Creek Hamlet Course</t>
         </is>
       </c>
       <c r="B407" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="D407" t="n">
-        <v>457</v>
+        <v>339</v>
       </c>
       <c r="E407" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F407" t="n">
-        <v>214</v>
+        <v>96</v>
       </c>
       <c r="G407" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="H407" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="I407" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J407" t="inlineStr">
         <is>
-          <t>No Issue</t>
+          <t>Focus on Tee Shot; Approach Shot</t>
         </is>
       </c>
       <c r="K407" t="inlineStr">
@@ -19458,18 +19454,18 @@
       </c>
       <c r="L407" t="inlineStr">
         <is>
-          <t>3H</t>
+          <t>SW</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Wind Watch Hamlet Course</t>
+          <t>Willow Creek Hamlet Course</t>
         </is>
       </c>
       <c r="B408" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C408" t="inlineStr">
         <is>
@@ -19477,16 +19473,16 @@
         </is>
       </c>
       <c r="D408" t="n">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="E408" t="n">
         <v>3</v>
       </c>
       <c r="F408" t="n">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="G408" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="H408" t="n">
         <v>0</v>
@@ -19501,7 +19497,7 @@
       </c>
       <c r="K408" t="inlineStr">
         <is>
-          <t>6I</t>
+          <t>8I</t>
         </is>
       </c>
       <c r="L408" t="inlineStr"/>
@@ -19509,25 +19505,25 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Wind Watch Hamlet Course</t>
+          <t>Willow Creek Hamlet Course</t>
         </is>
       </c>
       <c r="B409" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="D409" t="n">
-        <v>155</v>
+        <v>363</v>
       </c>
       <c r="E409" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F409" t="n">
-        <v>155</v>
+        <v>120</v>
       </c>
       <c r="G409" t="n">
         <v>2</v>
@@ -19536,28 +19532,32 @@
         <v>0</v>
       </c>
       <c r="I409" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J409" t="inlineStr">
         <is>
-          <t>Focus on Tee Shot (Change Strategy)</t>
+          <t>Work on Tee Shot (Change Strategy)</t>
         </is>
       </c>
       <c r="K409" t="inlineStr">
         <is>
-          <t>8I</t>
-        </is>
-      </c>
-      <c r="L409" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>GW</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Wind Watch Hamlet Course</t>
+          <t>Willow Creek Hamlet Course</t>
         </is>
       </c>
       <c r="B410" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C410" t="inlineStr">
         <is>
@@ -19565,26 +19565,26 @@
         </is>
       </c>
       <c r="D410" t="n">
-        <v>413</v>
+        <v>555</v>
       </c>
       <c r="E410" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F410" t="n">
-        <v>170</v>
+        <v>312</v>
       </c>
       <c r="G410" t="n">
         <v>2</v>
       </c>
       <c r="H410" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I410" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>Focus on Tee Shot; Approach Shot</t>
+          <t>Work on Tee Shot (Change Strategy)</t>
         </is>
       </c>
       <c r="K410" t="inlineStr">
@@ -19594,66 +19594,62 @@
       </c>
       <c r="L410" t="inlineStr">
         <is>
-          <t>7I</t>
+          <t>Layup (3H)</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Wind Watch Hamlet Course</t>
+          <t>Willow Creek Hamlet Course</t>
         </is>
       </c>
       <c r="B411" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="D411" t="n">
-        <v>408</v>
+        <v>172</v>
       </c>
       <c r="E411" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F411" t="n">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="G411" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="H411" t="n">
         <v>0</v>
       </c>
       <c r="I411" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J411" t="inlineStr">
         <is>
-          <t>Focus on Tee Shot; Approach Shot</t>
+          <t>No Issue</t>
         </is>
       </c>
       <c r="K411" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="L411" t="inlineStr">
-        <is>
           <t>7I</t>
         </is>
       </c>
+      <c r="L411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Wind Watch Hamlet Course</t>
+          <t>Willow Creek Hamlet Course</t>
         </is>
       </c>
       <c r="B412" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C412" t="inlineStr">
         <is>
@@ -19661,66 +19657,70 @@
         </is>
       </c>
       <c r="D412" t="n">
-        <v>169</v>
+        <v>527</v>
       </c>
       <c r="E412" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F412" t="n">
-        <v>169</v>
+        <v>284</v>
       </c>
       <c r="G412" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="H412" t="n">
         <v>0</v>
       </c>
       <c r="I412" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J412" t="inlineStr">
         <is>
-          <t>No Issue</t>
+          <t>Focus on Tee Shot; Approach Shot</t>
         </is>
       </c>
       <c r="K412" t="inlineStr">
         <is>
-          <t>7I</t>
-        </is>
-      </c>
-      <c r="L412" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>Layup (5I)</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Wind Watch Hamlet Course</t>
+          <t>Willow Creek Hamlet Course</t>
         </is>
       </c>
       <c r="B413" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="D413" t="n">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="E413" t="n">
         <v>3</v>
       </c>
       <c r="F413" t="n">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="G413" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="H413" t="n">
         <v>0</v>
       </c>
       <c r="I413" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J413" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
       </c>
       <c r="K413" t="inlineStr">
         <is>
-          <t>8I</t>
+          <t>PW</t>
         </is>
       </c>
       <c r="L413" t="inlineStr"/>
@@ -19737,11 +19737,11 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Wind Watch Hamlet Course</t>
+          <t>Willow Creek Hamlet Course</t>
         </is>
       </c>
       <c r="B414" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C414" t="inlineStr">
         <is>
@@ -19749,26 +19749,26 @@
         </is>
       </c>
       <c r="D414" t="n">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="E414" t="n">
         <v>4</v>
       </c>
       <c r="F414" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="G414" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="H414" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="I414" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J414" t="inlineStr">
         <is>
-          <t>Focus on Tee Shot; Approach Shot</t>
+          <t>No Issue</t>
         </is>
       </c>
       <c r="K414" t="inlineStr">
@@ -19778,38 +19778,38 @@
       </c>
       <c r="L414" t="inlineStr">
         <is>
-          <t>9I</t>
+          <t>8I</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Wind Watch Hamlet Course</t>
+          <t>Willow Creek Hamlet Course</t>
         </is>
       </c>
       <c r="B415" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="D415" t="n">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="E415" t="n">
         <v>4</v>
       </c>
       <c r="F415" t="n">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="G415" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="H415" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="I415" t="n">
         <v>0</v>
@@ -19826,7 +19826,7 @@
       </c>
       <c r="L415" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>9I</t>
         </is>
       </c>
     </row>
@@ -19837,7 +19837,7 @@
         </is>
       </c>
       <c r="B416" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C416" t="inlineStr">
         <is>
@@ -19845,16 +19845,16 @@
         </is>
       </c>
       <c r="D416" t="n">
-        <v>470</v>
+        <v>360</v>
       </c>
       <c r="E416" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F416" t="n">
-        <v>227</v>
+        <v>117</v>
       </c>
       <c r="G416" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="H416" t="n">
         <v>0</v>
@@ -19874,7 +19874,7 @@
       </c>
       <c r="L416" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -19885,7 +19885,7 @@
         </is>
       </c>
       <c r="B417" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C417" t="inlineStr">
         <is>
@@ -19893,16 +19893,16 @@
         </is>
       </c>
       <c r="D417" t="n">
-        <v>468</v>
+        <v>359</v>
       </c>
       <c r="E417" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F417" t="n">
-        <v>225</v>
+        <v>116</v>
       </c>
       <c r="G417" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="H417" t="n">
         <v>0.5</v>
@@ -19922,7 +19922,7 @@
       </c>
       <c r="L417" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>GW</t>
         </is>
       </c>
     </row>
@@ -19933,7 +19933,7 @@
         </is>
       </c>
       <c r="B418" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C418" t="inlineStr">
         <is>
@@ -19941,16 +19941,16 @@
         </is>
       </c>
       <c r="D418" t="n">
-        <v>306</v>
+        <v>480</v>
       </c>
       <c r="E418" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F418" t="n">
-        <v>63</v>
+        <v>237</v>
       </c>
       <c r="G418" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="H418" t="n">
         <v>0</v>
@@ -19960,7 +19960,7 @@
       </c>
       <c r="J418" t="inlineStr">
         <is>
-          <t>Focus on Tee Shot; Approach Shot</t>
+          <t>Focus on Approach (Change Strategy)</t>
         </is>
       </c>
       <c r="K418" t="inlineStr">
@@ -19970,7 +19970,7 @@
       </c>
       <c r="L418" t="inlineStr">
         <is>
-          <t>LW</t>
+          <t>Layup (5I)</t>
         </is>
       </c>
     </row>
@@ -19981,7 +19981,7 @@
         </is>
       </c>
       <c r="B419" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C419" t="inlineStr">
         <is>
@@ -19989,36 +19989,36 @@
         </is>
       </c>
       <c r="D419" t="n">
-        <v>282</v>
+        <v>440</v>
       </c>
       <c r="E419" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F419" t="n">
-        <v>66</v>
+        <v>197</v>
       </c>
       <c r="G419" t="n">
+        <v>2</v>
+      </c>
+      <c r="H419" t="n">
         <v>1</v>
       </c>
-      <c r="H419" t="n">
-        <v>0</v>
-      </c>
       <c r="I419" t="n">
         <v>0</v>
       </c>
       <c r="J419" t="inlineStr">
         <is>
-          <t>Focus on Tee Shot; Approach Shot</t>
+          <t>Focus on Approach (Change Strategy)</t>
         </is>
       </c>
       <c r="K419" t="inlineStr">
         <is>
-          <t>3W</t>
+          <t>D</t>
         </is>
       </c>
       <c r="L419" t="inlineStr">
         <is>
-          <t>LW</t>
+          <t>3H</t>
         </is>
       </c>
     </row>
@@ -20029,7 +20029,7 @@
         </is>
       </c>
       <c r="B420" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C420" t="inlineStr">
         <is>
@@ -20037,16 +20037,16 @@
         </is>
       </c>
       <c r="D420" t="n">
-        <v>148</v>
+        <v>315</v>
       </c>
       <c r="E420" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F420" t="n">
-        <v>148</v>
+        <v>72</v>
       </c>
       <c r="G420" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="H420" t="n">
         <v>0</v>
@@ -20056,15 +20056,19 @@
       </c>
       <c r="J420" t="inlineStr">
         <is>
-          <t>Focus on Tee Shot (Change Strategy)</t>
+          <t>Focus on Tee Shot; Approach Shot</t>
         </is>
       </c>
       <c r="K420" t="inlineStr">
         <is>
-          <t>9I</t>
-        </is>
-      </c>
-      <c r="L420" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>LW</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -20073,7 +20077,7 @@
         </is>
       </c>
       <c r="B421" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C421" t="inlineStr">
         <is>
@@ -20081,34 +20085,38 @@
         </is>
       </c>
       <c r="D421" t="n">
-        <v>123</v>
+        <v>325</v>
       </c>
       <c r="E421" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F421" t="n">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="G421" t="n">
         <v>2</v>
       </c>
       <c r="H421" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I421" t="n">
         <v>0</v>
       </c>
       <c r="J421" t="inlineStr">
         <is>
-          <t>Focus on Tee Shot (Change Strategy)</t>
+          <t>Focus on Tee Shot; Approach Shot</t>
         </is>
       </c>
       <c r="K421" t="inlineStr">
         <is>
-          <t>GW</t>
-        </is>
-      </c>
-      <c r="L421" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>LW</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -20117,7 +20125,7 @@
         </is>
       </c>
       <c r="B422" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C422" t="inlineStr">
         <is>
@@ -20125,26 +20133,26 @@
         </is>
       </c>
       <c r="D422" t="n">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E422" t="n">
         <v>4</v>
       </c>
       <c r="F422" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G422" t="n">
         <v>2</v>
       </c>
       <c r="H422" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I422" t="n">
         <v>0</v>
       </c>
       <c r="J422" t="inlineStr">
         <is>
-          <t>No Issue</t>
+          <t>Focus on Tee Shot; Approach Shot</t>
         </is>
       </c>
       <c r="K422" t="inlineStr">
@@ -20165,7 +20173,7 @@
         </is>
       </c>
       <c r="B423" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C423" t="inlineStr">
         <is>
@@ -20173,26 +20181,26 @@
         </is>
       </c>
       <c r="D423" t="n">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="E423" t="n">
         <v>4</v>
       </c>
       <c r="F423" t="n">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="G423" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="H423" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I423" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J423" t="inlineStr">
         <is>
-          <t>No Issue</t>
+          <t>Focus on Tee Shot; Approach Shot</t>
         </is>
       </c>
       <c r="K423" t="inlineStr">
@@ -20213,7 +20221,7 @@
         </is>
       </c>
       <c r="B424" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C424" t="inlineStr">
         <is>
@@ -20221,34 +20229,38 @@
         </is>
       </c>
       <c r="D424" t="n">
-        <v>218</v>
+        <v>478</v>
       </c>
       <c r="E424" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F424" t="n">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="G424" t="n">
         <v>2</v>
       </c>
       <c r="H424" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I424" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J424" t="inlineStr">
         <is>
-          <t>Focus on Tee Shot (Change Strategy)</t>
+          <t>No Issue</t>
         </is>
       </c>
       <c r="K424" t="inlineStr">
         <is>
-          <t>3W</t>
-        </is>
-      </c>
-      <c r="L424" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>Layup (5I)</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -20257,7 +20269,7 @@
         </is>
       </c>
       <c r="B425" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C425" t="inlineStr">
         <is>
@@ -20265,34 +20277,38 @@
         </is>
       </c>
       <c r="D425" t="n">
-        <v>194</v>
+        <v>457</v>
       </c>
       <c r="E425" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F425" t="n">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="G425" t="n">
         <v>1.5</v>
       </c>
       <c r="H425" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I425" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J425" t="inlineStr">
         <is>
-          <t>Focus on Tee Shot (Change Strategy)</t>
+          <t>No Issue</t>
         </is>
       </c>
       <c r="K425" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
           <t>3H</t>
         </is>
       </c>
-      <c r="L425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -20301,7 +20317,7 @@
         </is>
       </c>
       <c r="B426" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C426" t="inlineStr">
         <is>
@@ -20309,38 +20325,34 @@
         </is>
       </c>
       <c r="D426" t="n">
-        <v>543</v>
+        <v>177</v>
       </c>
       <c r="E426" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F426" t="n">
-        <v>300</v>
+        <v>177</v>
       </c>
       <c r="G426" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="H426" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I426" t="n">
         <v>0</v>
       </c>
       <c r="J426" t="inlineStr">
         <is>
-          <t>Focus on Tee Shot; Approach Shot</t>
+          <t>Focus on Tee Shot (Change Strategy)</t>
         </is>
       </c>
       <c r="K426" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="L426" t="inlineStr">
-        <is>
-          <t>Layup (3H)</t>
-        </is>
-      </c>
+          <t>6I</t>
+        </is>
+      </c>
+      <c r="L426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -20349,7 +20361,7 @@
         </is>
       </c>
       <c r="B427" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C427" t="inlineStr">
         <is>
@@ -20357,13 +20369,13 @@
         </is>
       </c>
       <c r="D427" t="n">
-        <v>545</v>
+        <v>155</v>
       </c>
       <c r="E427" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F427" t="n">
-        <v>302</v>
+        <v>155</v>
       </c>
       <c r="G427" t="n">
         <v>2</v>
@@ -20376,19 +20388,15 @@
       </c>
       <c r="J427" t="inlineStr">
         <is>
-          <t>Focus on Tee Shot; Approach Shot</t>
+          <t>Focus on Tee Shot (Change Strategy)</t>
         </is>
       </c>
       <c r="K427" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="L427" t="inlineStr">
-        <is>
-          <t>Layup (3H)</t>
-        </is>
-      </c>
+          <t>8I</t>
+        </is>
+      </c>
+      <c r="L427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -20397,7 +20405,7 @@
         </is>
       </c>
       <c r="B428" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C428" t="inlineStr">
         <is>
@@ -20405,26 +20413,26 @@
         </is>
       </c>
       <c r="D428" t="n">
-        <v>316</v>
+        <v>413</v>
       </c>
       <c r="E428" t="n">
         <v>4</v>
       </c>
       <c r="F428" t="n">
-        <v>73</v>
+        <v>170</v>
       </c>
       <c r="G428" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="H428" t="n">
         <v>0</v>
       </c>
       <c r="I428" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J428" t="inlineStr">
         <is>
-          <t>Work on Tee Shot (Change Strategy)</t>
+          <t>Focus on Tee Shot; Approach Shot</t>
         </is>
       </c>
       <c r="K428" t="inlineStr">
@@ -20434,7 +20442,7 @@
       </c>
       <c r="L428" t="inlineStr">
         <is>
-          <t>LW</t>
+          <t>7I</t>
         </is>
       </c>
     </row>
@@ -20445,7 +20453,7 @@
         </is>
       </c>
       <c r="B429" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C429" t="inlineStr">
         <is>
@@ -20453,26 +20461,26 @@
         </is>
       </c>
       <c r="D429" t="n">
-        <v>306</v>
+        <v>408</v>
       </c>
       <c r="E429" t="n">
         <v>4</v>
       </c>
       <c r="F429" t="n">
-        <v>63</v>
+        <v>165</v>
       </c>
       <c r="G429" t="n">
         <v>1.5</v>
       </c>
       <c r="H429" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I429" t="n">
         <v>0</v>
       </c>
       <c r="J429" t="inlineStr">
         <is>
-          <t>Work on Tee Shot (Change Strategy)</t>
+          <t>Focus on Tee Shot; Approach Shot</t>
         </is>
       </c>
       <c r="K429" t="inlineStr">
@@ -20482,7 +20490,7 @@
       </c>
       <c r="L429" t="inlineStr">
         <is>
-          <t>LW</t>
+          <t>7I</t>
         </is>
       </c>
     </row>
@@ -20493,7 +20501,7 @@
         </is>
       </c>
       <c r="B430" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C430" t="inlineStr">
         <is>
@@ -20501,38 +20509,34 @@
         </is>
       </c>
       <c r="D430" t="n">
-        <v>419</v>
+        <v>169</v>
       </c>
       <c r="E430" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F430" t="n">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="G430" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="H430" t="n">
         <v>0</v>
       </c>
       <c r="I430" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J430" t="inlineStr">
         <is>
-          <t>Focus on Tee Shot; Approach Shot</t>
+          <t>No Issue</t>
         </is>
       </c>
       <c r="K430" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="L430" t="inlineStr">
-        <is>
-          <t>6I</t>
-        </is>
-      </c>
+          <t>7I</t>
+        </is>
+      </c>
+      <c r="L430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -20541,7 +20545,7 @@
         </is>
       </c>
       <c r="B431" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C431" t="inlineStr">
         <is>
@@ -20549,16 +20553,16 @@
         </is>
       </c>
       <c r="D431" t="n">
-        <v>405</v>
+        <v>154</v>
       </c>
       <c r="E431" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F431" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="G431" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H431" t="n">
         <v>0</v>
@@ -20568,19 +20572,15 @@
       </c>
       <c r="J431" t="inlineStr">
         <is>
-          <t>Focus on Tee Shot; Approach Shot</t>
+          <t>No Issue</t>
         </is>
       </c>
       <c r="K431" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="L431" t="inlineStr">
-        <is>
           <t>8I</t>
         </is>
       </c>
+      <c r="L431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -20589,7 +20589,7 @@
         </is>
       </c>
       <c r="B432" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C432" t="inlineStr">
         <is>
@@ -20597,16 +20597,16 @@
         </is>
       </c>
       <c r="D432" t="n">
-        <v>324</v>
+        <v>390</v>
       </c>
       <c r="E432" t="n">
         <v>4</v>
       </c>
       <c r="F432" t="n">
-        <v>81</v>
+        <v>147</v>
       </c>
       <c r="G432" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="H432" t="n">
         <v>0</v>
@@ -20626,7 +20626,7 @@
       </c>
       <c r="L432" t="inlineStr">
         <is>
-          <t>LW</t>
+          <t>9I</t>
         </is>
       </c>
     </row>
@@ -20637,7 +20637,7 @@
         </is>
       </c>
       <c r="B433" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C433" t="inlineStr">
         <is>
@@ -20645,16 +20645,16 @@
         </is>
       </c>
       <c r="D433" t="n">
-        <v>325</v>
+        <v>372</v>
       </c>
       <c r="E433" t="n">
         <v>4</v>
       </c>
       <c r="F433" t="n">
-        <v>82</v>
+        <v>129</v>
       </c>
       <c r="G433" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="H433" t="n">
         <v>0.5</v>
@@ -20673,6 +20673,854 @@
         </is>
       </c>
       <c r="L433" t="inlineStr">
+        <is>
+          <t>PW</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Wind Watch Hamlet Course</t>
+        </is>
+      </c>
+      <c r="B434" t="n">
+        <v>10</v>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D434" t="n">
+        <v>470</v>
+      </c>
+      <c r="E434" t="n">
+        <v>5</v>
+      </c>
+      <c r="F434" t="n">
+        <v>227</v>
+      </c>
+      <c r="G434" t="n">
+        <v>2</v>
+      </c>
+      <c r="H434" t="n">
+        <v>0</v>
+      </c>
+      <c r="I434" t="n">
+        <v>0</v>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>Focus on Tee Shot; Approach Shot</t>
+        </is>
+      </c>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>3W</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>Wind Watch Hamlet Course</t>
+        </is>
+      </c>
+      <c r="B435" t="n">
+        <v>10</v>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="D435" t="n">
+        <v>468</v>
+      </c>
+      <c r="E435" t="n">
+        <v>5</v>
+      </c>
+      <c r="F435" t="n">
+        <v>225</v>
+      </c>
+      <c r="G435" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H435" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I435" t="n">
+        <v>0</v>
+      </c>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>Focus on Tee Shot; Approach Shot</t>
+        </is>
+      </c>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>3W</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>Wind Watch Hamlet Course</t>
+        </is>
+      </c>
+      <c r="B436" t="n">
+        <v>11</v>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D436" t="n">
+        <v>306</v>
+      </c>
+      <c r="E436" t="n">
+        <v>4</v>
+      </c>
+      <c r="F436" t="n">
+        <v>63</v>
+      </c>
+      <c r="G436" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H436" t="n">
+        <v>0</v>
+      </c>
+      <c r="I436" t="n">
+        <v>0</v>
+      </c>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>Focus on Tee Shot; Approach Shot</t>
+        </is>
+      </c>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>LW</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Wind Watch Hamlet Course</t>
+        </is>
+      </c>
+      <c r="B437" t="n">
+        <v>11</v>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="D437" t="n">
+        <v>282</v>
+      </c>
+      <c r="E437" t="n">
+        <v>4</v>
+      </c>
+      <c r="F437" t="n">
+        <v>63</v>
+      </c>
+      <c r="G437" t="n">
+        <v>1</v>
+      </c>
+      <c r="H437" t="n">
+        <v>0</v>
+      </c>
+      <c r="I437" t="n">
+        <v>0</v>
+      </c>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>Focus on Tee Shot; Approach Shot</t>
+        </is>
+      </c>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>3W</t>
+        </is>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>LW</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Wind Watch Hamlet Course</t>
+        </is>
+      </c>
+      <c r="B438" t="n">
+        <v>12</v>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D438" t="n">
+        <v>148</v>
+      </c>
+      <c r="E438" t="n">
+        <v>3</v>
+      </c>
+      <c r="F438" t="n">
+        <v>148</v>
+      </c>
+      <c r="G438" t="n">
+        <v>2</v>
+      </c>
+      <c r="H438" t="n">
+        <v>0</v>
+      </c>
+      <c r="I438" t="n">
+        <v>0</v>
+      </c>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>Focus on Tee Shot (Change Strategy)</t>
+        </is>
+      </c>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>9I</t>
+        </is>
+      </c>
+      <c r="L438" t="inlineStr"/>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Wind Watch Hamlet Course</t>
+        </is>
+      </c>
+      <c r="B439" t="n">
+        <v>12</v>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="D439" t="n">
+        <v>123</v>
+      </c>
+      <c r="E439" t="n">
+        <v>3</v>
+      </c>
+      <c r="F439" t="n">
+        <v>123</v>
+      </c>
+      <c r="G439" t="n">
+        <v>2</v>
+      </c>
+      <c r="H439" t="n">
+        <v>0</v>
+      </c>
+      <c r="I439" t="n">
+        <v>0</v>
+      </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>Focus on Tee Shot (Change Strategy)</t>
+        </is>
+      </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>GW</t>
+        </is>
+      </c>
+      <c r="L439" t="inlineStr"/>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Wind Watch Hamlet Course</t>
+        </is>
+      </c>
+      <c r="B440" t="n">
+        <v>13</v>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D440" t="n">
+        <v>377</v>
+      </c>
+      <c r="E440" t="n">
+        <v>4</v>
+      </c>
+      <c r="F440" t="n">
+        <v>134</v>
+      </c>
+      <c r="G440" t="n">
+        <v>2</v>
+      </c>
+      <c r="H440" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I440" t="n">
+        <v>0</v>
+      </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>No Issue</t>
+        </is>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>PW</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Wind Watch Hamlet Course</t>
+        </is>
+      </c>
+      <c r="B441" t="n">
+        <v>13</v>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="D441" t="n">
+        <v>359</v>
+      </c>
+      <c r="E441" t="n">
+        <v>4</v>
+      </c>
+      <c r="F441" t="n">
+        <v>116</v>
+      </c>
+      <c r="G441" t="n">
+        <v>2</v>
+      </c>
+      <c r="H441" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I441" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>No Issue</t>
+        </is>
+      </c>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>GW</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Wind Watch Hamlet Course</t>
+        </is>
+      </c>
+      <c r="B442" t="n">
+        <v>14</v>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D442" t="n">
+        <v>218</v>
+      </c>
+      <c r="E442" t="n">
+        <v>3</v>
+      </c>
+      <c r="F442" t="n">
+        <v>218</v>
+      </c>
+      <c r="G442" t="n">
+        <v>2</v>
+      </c>
+      <c r="H442" t="n">
+        <v>0</v>
+      </c>
+      <c r="I442" t="n">
+        <v>0</v>
+      </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>Focus on Tee Shot (Change Strategy)</t>
+        </is>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>3H</t>
+        </is>
+      </c>
+      <c r="L442" t="inlineStr"/>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Wind Watch Hamlet Course</t>
+        </is>
+      </c>
+      <c r="B443" t="n">
+        <v>14</v>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="D443" t="n">
+        <v>194</v>
+      </c>
+      <c r="E443" t="n">
+        <v>3</v>
+      </c>
+      <c r="F443" t="n">
+        <v>194</v>
+      </c>
+      <c r="G443" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H443" t="n">
+        <v>0</v>
+      </c>
+      <c r="I443" t="n">
+        <v>0</v>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>Focus on Tee Shot (Change Strategy)</t>
+        </is>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>3H</t>
+        </is>
+      </c>
+      <c r="L443" t="inlineStr"/>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Wind Watch Hamlet Course</t>
+        </is>
+      </c>
+      <c r="B444" t="n">
+        <v>15</v>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D444" t="n">
+        <v>543</v>
+      </c>
+      <c r="E444" t="n">
+        <v>5</v>
+      </c>
+      <c r="F444" t="n">
+        <v>300</v>
+      </c>
+      <c r="G444" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H444" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I444" t="n">
+        <v>0</v>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>Focus on Tee Shot; Approach Shot</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>Layup (3H)</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>Wind Watch Hamlet Course</t>
+        </is>
+      </c>
+      <c r="B445" t="n">
+        <v>15</v>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="D445" t="n">
+        <v>545</v>
+      </c>
+      <c r="E445" t="n">
+        <v>5</v>
+      </c>
+      <c r="F445" t="n">
+        <v>302</v>
+      </c>
+      <c r="G445" t="n">
+        <v>2</v>
+      </c>
+      <c r="H445" t="n">
+        <v>0</v>
+      </c>
+      <c r="I445" t="n">
+        <v>0</v>
+      </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>Focus on Tee Shot; Approach Shot</t>
+        </is>
+      </c>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>Layup (3H)</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Wind Watch Hamlet Course</t>
+        </is>
+      </c>
+      <c r="B446" t="n">
+        <v>16</v>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D446" t="n">
+        <v>316</v>
+      </c>
+      <c r="E446" t="n">
+        <v>4</v>
+      </c>
+      <c r="F446" t="n">
+        <v>73</v>
+      </c>
+      <c r="G446" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H446" t="n">
+        <v>0</v>
+      </c>
+      <c r="I446" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>Work on Tee Shot (Change Strategy)</t>
+        </is>
+      </c>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>LW</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Wind Watch Hamlet Course</t>
+        </is>
+      </c>
+      <c r="B447" t="n">
+        <v>16</v>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="D447" t="n">
+        <v>306</v>
+      </c>
+      <c r="E447" t="n">
+        <v>4</v>
+      </c>
+      <c r="F447" t="n">
+        <v>63</v>
+      </c>
+      <c r="G447" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H447" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I447" t="n">
+        <v>0</v>
+      </c>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>Work on Tee Shot (Change Strategy)</t>
+        </is>
+      </c>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>LW</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Wind Watch Hamlet Course</t>
+        </is>
+      </c>
+      <c r="B448" t="n">
+        <v>17</v>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D448" t="n">
+        <v>419</v>
+      </c>
+      <c r="E448" t="n">
+        <v>4</v>
+      </c>
+      <c r="F448" t="n">
+        <v>176</v>
+      </c>
+      <c r="G448" t="n">
+        <v>2</v>
+      </c>
+      <c r="H448" t="n">
+        <v>0</v>
+      </c>
+      <c r="I448" t="n">
+        <v>0</v>
+      </c>
+      <c r="J448" t="inlineStr">
+        <is>
+          <t>Focus on Tee Shot; Approach Shot</t>
+        </is>
+      </c>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>6I</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Wind Watch Hamlet Course</t>
+        </is>
+      </c>
+      <c r="B449" t="n">
+        <v>17</v>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="D449" t="n">
+        <v>405</v>
+      </c>
+      <c r="E449" t="n">
+        <v>4</v>
+      </c>
+      <c r="F449" t="n">
+        <v>162</v>
+      </c>
+      <c r="G449" t="n">
+        <v>2</v>
+      </c>
+      <c r="H449" t="n">
+        <v>0</v>
+      </c>
+      <c r="I449" t="n">
+        <v>0</v>
+      </c>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>Focus on Tee Shot; Approach Shot</t>
+        </is>
+      </c>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>7I</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Wind Watch Hamlet Course</t>
+        </is>
+      </c>
+      <c r="B450" t="n">
+        <v>18</v>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D450" t="n">
+        <v>324</v>
+      </c>
+      <c r="E450" t="n">
+        <v>4</v>
+      </c>
+      <c r="F450" t="n">
+        <v>81</v>
+      </c>
+      <c r="G450" t="n">
+        <v>2</v>
+      </c>
+      <c r="H450" t="n">
+        <v>0</v>
+      </c>
+      <c r="I450" t="n">
+        <v>0</v>
+      </c>
+      <c r="J450" t="inlineStr">
+        <is>
+          <t>Focus on Tee Shot; Approach Shot</t>
+        </is>
+      </c>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>LW</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Wind Watch Hamlet Course</t>
+        </is>
+      </c>
+      <c r="B451" t="n">
+        <v>18</v>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="D451" t="n">
+        <v>325</v>
+      </c>
+      <c r="E451" t="n">
+        <v>4</v>
+      </c>
+      <c r="F451" t="n">
+        <v>82</v>
+      </c>
+      <c r="G451" t="n">
+        <v>2</v>
+      </c>
+      <c r="H451" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I451" t="n">
+        <v>0</v>
+      </c>
+      <c r="J451" t="inlineStr">
+        <is>
+          <t>Focus on Tee Shot; Approach Shot</t>
+        </is>
+      </c>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L451" t="inlineStr">
         <is>
           <t>LW</t>
         </is>
